--- a/BASE DE DATOS - COMPUTACIONAL.xlsx
+++ b/BASE DE DATOS - COMPUTACIONAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85ad1e88542dc0fc/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="968" documentId="8_{865165E8-6C42-4D48-93DB-5FEF425A3BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6DF3F28-6551-4CEE-BC0C-924352C3D585}"/>
+  <xr:revisionPtr revIDLastSave="1253" documentId="8_{865165E8-6C42-4D48-93DB-5FEF425A3BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FEFA1BB-8A9A-421E-8F0A-08CACCADCCE9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F7F6ACAE-8EDB-49D4-90A9-56CF5817301F}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="link" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="499">
   <si>
     <t>Canción</t>
   </si>
@@ -58,9 +57,6 @@
     <t>Temporada</t>
   </si>
   <si>
-    <t xml:space="preserve">Descripción del ep. </t>
-  </si>
-  <si>
     <t>Portada (imagen)</t>
   </si>
   <si>
@@ -160,12 +156,6 @@
     <t>Whistle On the River</t>
   </si>
   <si>
-    <t>The Mercy Brothers</t>
-  </si>
-  <si>
-    <t>You Don’t Mess Around With Jim</t>
-  </si>
-  <si>
     <t>Jim Croce</t>
   </si>
   <si>
@@ -196,9 +186,6 @@
     <t>Al Casey Combo</t>
   </si>
   <si>
-    <t>How I Feel About You</t>
-  </si>
-  <si>
     <t>"The Vanishing of Will Byers"</t>
   </si>
   <si>
@@ -304,9 +291,6 @@
     <t>Queen</t>
   </si>
   <si>
-    <t>Cameron Brooks</t>
-  </si>
-  <si>
     <t>There Is Frost On the Moon</t>
   </si>
   <si>
@@ -332,9 +316,6 @@
   </si>
   <si>
     <t>Bon Jovi</t>
-  </si>
-  <si>
-    <t>Giant Circles</t>
   </si>
   <si>
     <t>Back To Nature</t>
@@ -394,9 +375,6 @@
     <t>Metallica</t>
   </si>
   <si>
-    <t>Should I Stay or Should I Go</t>
-  </si>
-  <si>
     <t>The Way We Were</t>
   </si>
   <si>
@@ -418,9 +396,6 @@
     <t>I Shall Not Care</t>
   </si>
   <si>
-    <t>I See Charcoal (You See Scarlet)</t>
-  </si>
-  <si>
     <t>Jenny May</t>
   </si>
   <si>
@@ -547,9 +522,6 @@
     <t>Peter Gabriel</t>
   </si>
   <si>
-    <t>Jumpstreet</t>
-  </si>
-  <si>
     <t>“The Weirdo On Maple Street”</t>
   </si>
   <si>
@@ -562,12 +534,6 @@
     <t>Color Dreams</t>
   </si>
   <si>
-    <t>Should I Stay Or Should I Go (REPITE)</t>
-  </si>
-  <si>
-    <t>REPITE</t>
-  </si>
-  <si>
     <t>“The Flea And the Acrobat”</t>
   </si>
   <si>
@@ -583,24 +549,15 @@
     <t>Green Desert</t>
   </si>
   <si>
-    <t>Old Time Rock &amp; Roll</t>
-  </si>
-  <si>
     <t>Nocturnal Me</t>
   </si>
   <si>
     <t>Sunglasses at Night</t>
   </si>
   <si>
-    <t xml:space="preserve">Happy Jose </t>
-  </si>
-  <si>
     <t>Concerto for Violin</t>
   </si>
   <si>
-    <t>Brahm’s Lullaby (REPITE)</t>
-  </si>
-  <si>
     <t>The Bargain Store</t>
   </si>
   <si>
@@ -616,28 +573,16 @@
     <t>New Order</t>
   </si>
   <si>
-    <t>Joe Keery’s Steve Harrington</t>
-  </si>
-  <si>
     <t>Echo &amp; The Bunnymen</t>
   </si>
   <si>
     <t>Corey Hart</t>
   </si>
   <si>
-    <t>Kookie Freeman</t>
-  </si>
-  <si>
     <t>English Chamber Orchestra &amp; Dmitry Sitkovetsky</t>
   </si>
   <si>
     <t>Dolly Parton</t>
-  </si>
-  <si>
-    <t>SOLO SE HIZO PARA EL MOMENTO DE LA SERIE</t>
-  </si>
-  <si>
-    <t>s/a</t>
   </si>
   <si>
     <t>Fields of Coral</t>
@@ -717,9 +662,6 @@
     <t>“The Lost Sister”</t>
   </si>
   <si>
-    <t>en clase preguntar: descripcion por cada escena en la que la cancion aparece o general (sinoptica) acerca del episodio</t>
-  </si>
-  <si>
     <t>Tercera</t>
   </si>
   <si>
@@ -753,9 +695,6 @@
     <t>Rock This Town</t>
   </si>
   <si>
-    <t>Brian Setzer</t>
-  </si>
-  <si>
     <t>Moving In Stereo</t>
   </si>
   <si>
@@ -828,9 +767,6 @@
     <t>We’ll Meet Again</t>
   </si>
   <si>
-    <t>APM Music</t>
-  </si>
-  <si>
     <t>Miss Sophisticate</t>
   </si>
   <si>
@@ -1011,18 +947,12 @@
     <t>“Suzie, Do You Copy?”</t>
   </si>
   <si>
-    <t xml:space="preserve">“Einstein Disintegrated” – From Back To The Future Original Score </t>
-  </si>
-  <si>
     <t>Wien Bleibt Wien/”Vienna Forever Vienna</t>
   </si>
   <si>
     <t>Doc Returns – From Back to the Future Original Score</t>
   </si>
   <si>
-    <t>Man on the Flying Trapeze</t>
-  </si>
-  <si>
     <t>In the Good Old Summertime</t>
   </si>
   <si>
@@ -1044,9 +974,6 @@
     <t>Andrew Pilmer</t>
   </si>
   <si>
-    <t>Wurlitzer</t>
-  </si>
-  <si>
     <t>Wurlitzer 146 Carousel Organ</t>
   </si>
   <si>
@@ -1071,9 +998,6 @@
     <t>Deep</t>
   </si>
   <si>
-    <t>Heroes</t>
-  </si>
-  <si>
     <t>Peter Sandberg</t>
   </si>
   <si>
@@ -1095,18 +1019,9 @@
     <t>Yello</t>
   </si>
   <si>
-    <t>1889 (Años de publicacion antiguos)</t>
-  </si>
-  <si>
-    <t>1899 (AÑO DE COMPOSICION- QUE HACER?)</t>
-  </si>
-  <si>
     <t>Bonnie Tyler</t>
   </si>
   <si>
-    <t>1867 (composicion) - publicacion asociada (1959)</t>
-  </si>
-  <si>
     <t>Smart Remarks</t>
   </si>
   <si>
@@ -1120,13 +1035,556 @@
   </si>
   <si>
     <t>https://www.google.com/imgres?q=Talking%20In%20Your%20Sleep%09The%20Romantics%0D%0A&amp;imgurl=https%3A%2F%2Fupload.wikimedia.org%2Fwikipedia%2Fen%2F0%2F0a%2FThe_romantics-talking_in_your_sleep_s.jpg&amp;imgrefurl=https%3A%2F%2Fen.wikipedia.org%2Fwiki%2FTalking_in_Your_Sleep_(The_Romantics_song)&amp;docid=9pp60CM4E4S99M&amp;tbnid=TVKJOnLmoOQXaM&amp;vet=12ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA..i&amp;w=315&amp;h=317&amp;hcb=2&amp;ved=2ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273ac8529be93467378a0272698</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e029a8821caefd5274d1b540d20</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273efd94e4e17a355f43d3af543</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273fcb35a573a3811f1a67e15a6</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2736a74089537c2dbd548c4a95e</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273d6ff6fdab2d614a6a2e813ce</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273c1c008d9732f0ee4b7e38fce</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2735ff314d0f53d4dcdc3c851aa</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273ebd6d20c0082524244ef83df</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e0209d3e95496661b50eefd0bc6</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27329da474f1a0f9527434797ea</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273280b72ca76b4734debfc190e</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e02c1aa0a815eae4ac2a5eaa301</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTRMJNjd4V7iZPnIQmKKOWOiuTYJSOKcSuSxqx6eyXk8Q&amp;s</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273d9c466ee1473de38c0356d3e</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273fb138543b1f04635a88ac7e5</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRP6LAI69rsBMje072aHsvkVV14Ly1limesjJq1lnaW9kQHTzNelbpCDGZG&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27378ef535f6a126e85b9928cf1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BZjM3YTVmM2UtZDI4Ni00YWU0LTk4YzktMTc4NTAzYjg4NWY5XkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BOTQ5N2IxN2QtYjU5Yy00Nzc5LThlZmQtODdmYzVlMDk2ZWQzXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
+  </si>
+  <si>
+    <t>https://images.zoogletools.com/s:bzglfiles/u/278585/b66e103f485a765923be75f3bb080e7afaafa3bf/original/joel-evans-as-heard-on-tv-600x-v-2.jpg/!!/meta%3AeyJzcmNCdWNrZXQiOiJiemdsZmlsZXMifQ%3D%3D.png</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2733f12c57d6248a5e307667d0d</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSjL2d40vIilzvWx1PGSMv9NKf2Qm7SOTLB109Wn1x4YGRWxCUUGDnJqik&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://www.serendeepity.net/wp-content/uploads/2020/06/joy-division-atmosphere.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2731b9b7ec714addecf64f14c09</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/d/db/New_Order_-_Elegia.webp</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273625913e87914d7f2bca59f85</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2739f2b3ff8acc0a0b83739e3b4</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQuVAmJtMHHHn-ngrQED3gDxUI3hNNlcIMj0JtqFxxAujCSQYMuKDbUH1o&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/images/g/rCQAAOSwEX1mLfZW/s-l1200.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27375d5abdad824712d3aca12d2</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27390f5de101324fcb3e91dae66</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27319e0fafc3891cb45745b680c</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2730aeb098073c62f4ea8703724</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273433c5ef2747f10a9e0b27eb0</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e0280174f67fa0fe00b42771580</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTEZFH5LfusT5jtRtmzbowSuSbRAVAtgGTNiODsSt8hSUZezKvyc2CLgic&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BMGJhNTI2MTEtZTcyOC00NzQ1LWJiZGEtNTllYjBhNzJhMTMyXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSb5M7Kug5soYe2MUXdfQf1JHyVLedug-QJS-QiK5uhhnS0JaAaN-9f-3Iu&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQVJq6bIeqyFQIzsd4pSw3RP7_U6bGCVgA-qQWC-72vQQ&amp;s</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQEIuYhFpW4UK-OATNq3KWcHbplpt_shI8KowhV5lOucWysjcf1wAcwgSy5&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR0fGNvQaGCMf-kJoyQOmgYdEnfvR-O81-hvn3zr_sbt1_6hFxL2Mejfe7G&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e0292f796d8a1aaf0f3b6e48801</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27332d1c00a69d70510d18a032e</t>
+  </si>
+  <si>
+    <t>https://f4.bcbits.com/img/a2318044756_16.jpg</t>
+  </si>
+  <si>
+    <t>https://f4.bcbits.com/img/a2997093668_10.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BYjAxMTJlNjMtYWYxOC00YzM3LWE1ODItM2QzMmVlMzU3ZTI4XkEyXkFqcGc@._V1_.jpg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQQ58TAb0ik16iOyDQOic0pqlEOE0H7pTq9rLE64n4ZCWnwERx1Nz8j4FX7&amp;s=10</t>
+  </si>
+  <si>
+    <t>The Mercey Brothers</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/FQ9mf7t8xeLTWs6ttHU7lELPGdIfRVHv_n7PEfMcfe0/rs:fit/g:sm/q:90/h:600/w:600/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE0MjY4/MTMwLTE1NzEwODk4/NDMtMTk0My5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27398078d325c25a5ac4081cfba</t>
+  </si>
+  <si>
+    <t>https://images.genius.com/3540b85e2bf50ece6440196ae331e2ee.600x600x1.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/7/71/The_Ghost_In_You_CD_Single.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e0284693ffbb1baef7ac35246af</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51Gg-HLIVmL._UXNaN_FMjpg_QL85_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51VvQY8luWL._UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273e22ada330eea886d311a3946</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTobu-346gr-dgjvO9nARkuqkGIdlUJuUMB6LOoeSyhOdCPshPTJVwKgHY&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/KCt4DQ_Nh-zXZB9fXKm-XxMRTGXCP8jvXCkD7Gw_fMw/rs:fit/g:sm/q:90/h:600/w:598/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTczMjU1/MzItMTQ2NjgwOTc5/NS0xOTgxLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/uWgp4b-4CGHHV-cGazlVeWbSU8J5nMvtYbMZx_QxOn4/rs:fit/g:sm/q:90/h:600/w:600/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM0NDUx/MDgtMTMzMDY1OTgw/Ni5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2737382902eb734966598a99b05</t>
+  </si>
+  <si>
+    <t>https://i1.sndcdn.com/artworks-csEi6P20byRY-0-t500x500.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2734b534faec4e24feaa42b3540</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/DA7z-3vYOWX9XEqnr91g7teKbSNRplMvxmqIPSqjrEc/rs:fit/g:sm/q:90/h:600/w:600/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTY3Mjk4/NjQtMTU2MzEzNzUw/OC02MjQ1LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://i1.sndcdn.com/artworks-000241231106-xv4dts-t500x500.jpg</t>
+  </si>
+  <si>
+    <t>https://images.genius.com/e84343de965bac690a19dd43dc90708a.592x592x1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/UjLns9nuf94NUVfjbcMG6de1TXedFF51EtXGSvxdDpA/rs:fit/g:sm/q:90/h:480/w:523/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM3NDQ1/MzktMTM0MjYyMjgz/Ny01MzcxLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273f4c4f8c2b77d5adbf60cb1ce</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/a/a0/HammerQueen.jpg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ3MLbgN-OOVenS7f6Kqm1pl7zjDGYc0vcib-y3rzPLTw&amp;s</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273ed68e46256e2e94aeed37843</t>
+  </si>
+  <si>
+    <t>https://images.genius.com/b8fcf48de91824b22a123c0d8e12c93a.598x599x1.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/d/da/Round_and_Round_%28Ratt_single_-_cover_art%29.jpg/250px-Round_and_Round_%28Ratt_single_-_cover_art%29.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/9/9d/Bon_Jovi_Runaway.JPG</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/qaqEqk_6pt6y65qjM-o1o0qLDQ7GjhDrLp0tjFc75FE/rs:fit/g:sm/q:90/h:598/w:600/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIyNzM2/NjYwLTE2NDg5MTE0/MDQtNTc4OC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e026c8b3f3599f9675600c77f52</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/91HriExE6cS._UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://ianmcnabb.yolasite.com/resources/birdsfly17.jpeg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSvgediYPwKI7Oq2NNQFHRn1FWvOzZ-Jlv6m9opblahzBESzR2_TYmsaHVD&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/-zKOhVSERS8/hq720.jpg?sqp=-oaymwEhCK4FEIIDSFryq4qpAxMIARUAAAAAGAElAADIQj0AgKJD&amp;rs=AOn4CLAxfjz5jObahTCrmgKPWCbPK5edaQ</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/b/b3/Barbra_Streisand_%22The_Way_We_Were%22.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273b33c99d166f15236efd104e6</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273bb16e0ec8372e63b90c4cb75</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273b6a828698993ac84d4f0b1de</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/3/32/Pat_Benatar_Love_is_a_Battlefield.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BMTM4NzlmYWYtZDhmYy00M2YxLTg4Y2YtYWNiMDBjNzYxYWVkXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
+  </si>
+  <si>
+    <t>https://images.genius.com/c4abb425a8a52dfd190f59541bf19a6e.1000x1000x1.png</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRjJ8W_h3ZzDboBEPySvpDrt5Z5jHNf8BqxAclsqyIUTm0LXeyHExREpQdN&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BNmZmMjExYzAtY2MwZi00ZmE3LWJmOGYtZDA4ZGM3ZjVlZjBlXkEyXkFqcGc@._V1_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51Ap59ji1wL._UXNaN_FMjpg_QL85_.jpg</t>
+  </si>
+  <si>
+    <t>Brian Setzer (Stray Cats)</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/d/de/Rock_This_TownUS45.jpg/250px-Rock_This_TownUS45.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/y5oPZFDci80/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT5GkkUX5POc9wjdwDKobhxMcNVls5yafMGhaZN91qTtw&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT2MqRUtBitM0hEelVkgCpx6kSYX2jbNWIGAqrzrgNwwCqm9At3cD-OB5w&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRbxH_eaM3XFz2NV1DtaaqxjU-oN8Vbcz2Szt8LIaJhGi4ccZ4zU5aHs-yN&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/0/02/Can%27t_Fight_This_Feeling_Cover_Art.jpg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSPmKCPTWL2ULtMSDWKS7lx8vQ2UTBUjYfOgPoPKOcbC8xyXJSDh5YmXrk&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTtcfUMI_ZSKIH8Pqgc4C-uB8ya7ksjwalvqM_aZV4P1A&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/CiUZmqrPoh9YzSsKkuhYOZsA27_MWDH-KXQ7SklxoJE/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM5ODYz/NDItMTM1MTQ0OTA5/Ny0xMTAyLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://spintimerecords.com/cdn/shop/files/LP-SenselessOfferings-frt_600x600_crop_center.jpg?v=1733281435</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2733c696470ebbe79c63bd4cdf2</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT1Mli58-tqVlnpavuNoetUy-lVWpgwjSZc6D2TqZbuWw9dYPbGhKfWUag&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273d3c58ce65006bac676c6f1e3</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/3/3f/Foreigner_-_Cold_As_Ice_b-w_I_Need_You_%281977%29.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273f1d95f4dbd086792e3ea5aa3</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/JVCZ2hMSXrvK-SYAHqz5YRE3p3c91kVfeNSNbaNKQnA/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQwNjc2/MTYtMTQxOTcyNDEx/Ni0xMjIxLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRvgfuONCcksV1J0G5xe1yCU3E_p-7JKg6JFmahdBNCBTcQ08vmEth1zHgT&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSO824HWidGjvIYaAnpGGFZY0v_KdjxlaUwyMIlL7lBYBVbjpGkO72Ikkg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWtV90L9duRJYkFpe4tSbT5bvzYKaJ-WlgpJWOOojvIg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2738862812335ec8ba255743d2b</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/2/2e/Things_Can_Only_Get_Better.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2731e8bd35d4a4e22055f8ebefb</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/a/a5/Wake_Me_Up_Before_You_Go-Go_-_Wham%21.jpg/250px-Wake_Me_Up_Before_You_Go-Go_-_Wham%21.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/jIK31Km6sbc/hq720.jpg?sqp=-oaymwEhCK4FEIIDSFryq4qpAxMIARUAAAAAGAElAADIQj0AgKJD&amp;rs=AOn4CLCkmfsXtlWIy-lJSVtVGE3DwvHBzQ</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/b/b9/American_Pie_by_Don_McLean.png</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27348a25133da05c22386875073</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/l-wKC4veQVo/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2732f83b15da2ebf22508caec70</t>
+  </si>
+  <si>
+    <t>https://i1.sndcdn.com/artworks-0qVSkg5vcKgT-0-t500x500.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b27333e899346d4f354e2c9b6d3f</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273407a515c79537d3078c325ed</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/9PMNb-n7qAI/sddefault.jpg?sqp=-oaymwEmCIAFEOAD8quKqQMa8AEB-AH-BIAC4AOKAgwIABABGGUgXShVMA8=&amp;rs=AOn4CLAB0z8_xY7F4ZYa8m2AJ9e38n7zVA</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/2OnonmQhG4bNt-J6vc0WjpmWMvY2diX8uMfwYSy9K1s/rs:fit/g:sm/q:90/h:600/w:600/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQ5MjI1/ODYtMTM3OTUyMzM0/NC04NTkzLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273bab70eaa17669293bfc00d90</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSUV1Ny4yx0gnPDEW1YWzPM7zHAaa0HpSOeUqnXXm22b2LYC431gHs9xFoK&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2730d62672a4c5da967ab776ce8</t>
+  </si>
+  <si>
+    <t>https://images.genius.com/0577c3a538128e1ab5ce1202f013c4a5.1000x1000x1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e02efd94e4e17a355f43d3af543</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTymFiyeX3x2a3CPUWO4eN4V1kKrGaOlHqjw0JcY6feBA&amp;s</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2737df5c3f6d40608eb756e7923</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQE7w8SZfHB0kmmSDFf3g2EgGybj65FNOwel2yoH7kneQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQwNWJ2ubZDXtlvftoIofDh3TtyihaFafrpfgFikJzU8w&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2737e48b42505bf47508f3474d8</t>
+  </si>
+  <si>
+    <t>https://d2oet5a29f64lj.cloudfront.net/img-data/w/240/album/600/XXL012.jpg</t>
+  </si>
+  <si>
+    <t>https://www.alfred.com/cdn/shop/files/00-26719_large_8ae9d2da-0ac0-4d5c-80a0-bbd1cf3be941.jpg?v=1779255503&amp;width=3840</t>
+  </si>
+  <si>
+    <t>John Philip Sousa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einstein Disintegrated – From Back To The Future Original Score </t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273364fb8debdc761097f6e87ed</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/0/09/Total_Eclipse_of_the_Heart_-_single_cover.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273915f37d6b3a47e2819c3db4e</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSkWbuttywTjl9iC5rJsBUnNUpc3apQd-UG10oqSm5AkQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b2730d2a01f6043b55c3fa37c2c7</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273e7ba7ec8dbf10a6db596cfe7</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxMSEhUTExQWFRUXGB0XFxgYFR0aHRggGRoaHxobGR0iHighHyImHRghITEhJSkrLi4uGyAzODMtNygtLisBCgoKDg0OGhAQGi0lHR8tKy0tLS0tLS0tLS0tKy0tLS0tLS0tLS0tLTAtLS0rLS0tLS0tLS4wLS8tLS0tKy0tLf/AABEIAKgBLAMBEQACEQEDEQH/xAAbAAEAAgMBAQAAAAAAAAAAAAAABQYDBAcCAf/EAE4QAAIBAgQCBgUFDAcHBQEAAAECEQADBBIhMQVBBhMiUWFxByMygaEUQpGx0TNDUlNic4KSk8Hh8BUXNHKjs9IWNVSUssLTJWOi4vEk/8QAGwEBAAMBAQEBAAAAAAAAAAAAAAECAwQFBgf/xABAEQACAQIEAgcFBQYEBwAAAAAAAQIDEQQSITEFURMUM0FhcYEiMpGh0RVTscHwBhY0UuHxIzVCskNUYnJzktL/2gAMAwEAAhEDEQA/AOW1zHvCgFAKAUAoBQCgOy8L4scLwjDXVUMcqiCYGpNUqScY3RhhMJHFYt0pOy1ZHj0jXPxNv9Y1j08uR7f7t0fvH8ESeH6YYi5YF23YRib3VEZ4EkJk3PMtHhFaRqSkr277Hn4jhVCjWdOU2/YctEu6918tDziunjor+p7VuQ2aQpIuZewfnCN45yKh1Xy/V7E0+DUpu3Sctt9YqWun4X+Jjx/pAuWykWkOa1buasdM6BiPdNJVpJ6I3wvAaVaDk5tWbWy7nY1v6y7v4m3+uar1iXI6P3bo/eP4If1lXfxNv9c06xLkP3bo/eP4I+f1lXPxNv8AXNOsS5D92qP3j+CA9JVz8Tb/AFzTrEuQ/dqj94/gj7/WXd/E2/1zTrEuQ/dqj94/gj6npIuEgdTb1Me0adYlyKv9m6KTfSP4I6QDXYfImLFnsGhKI20wFnwLt9dQWIriOJy21bsqgUksxACgEDc+YoD5wvGC4M3WBwGIBUmBAUxJ33qQaWOvBSOsdszDkmbKC2UMTOk9/nREEgiuAFzA9ogE6bBP3yffQk18Djesudl8xG4IYGJ3hh3nlQgsGHunre4BgJnwH21APnBTNxm/Lf8A6jUkPY5J6Xv95P8Am7f1VSW56WE7P1ZS6g6RQCgFAKAUAoBQCgFAKAUAoBQCgFAdVvNHBMPop0T2lDDc8iCKpVk4xuiOG4elXxzhVjdWejKh1v5Fr9ha/wBFc/TVP5mfUfYuA+5ibOG4tdtrlQqq5g+UWrcZhENGWMwga76VHS1OY+xsDa3RL5/UtXRnjVjEMuHxOHsEmcjdUsElixBWIBLS0jcnvrelXbdmeBxXgUaNN1qOy3T/ABRDdMsqYy4i27QVBbVR1Ns5QLaQBK7DuqlWrNTaTO7hXDMJWwkJ1KacnfV+bIXrfyLX7C1/oqnTVP5mej9i4D7mI678i1+wtf6KdNU/mY+xcB9zEs3F8JaTh2GurZsi47QzdRbk+3v2fAVrOrPo4u+p4mF4dhZ8RrUpU04xWi5bFZ678i1+wtf6Ky6ap/Mz2/sXAfcxM+Gx2QybOGcdz4a0R8FB+NSsRUXeZVOA4Cat0dvIvPRXEcPxRyHB4a3eAmOpSGjmpy8u769a6aVfPo9z5jiXBXg/bjrDnbVef1LzWp5Jhxx9WaBENZu+p8ncAd1CxpcXbLhSe5AfitECO6Nu5SRoOsbfU7idp5VLIRq9KOkCYe8ltlkMoLmN17cQZ07cE+A8KJXIbLTJYqUIjee8ECKgkhejJm85I+Yf8z+FSwWO003suvaYfFRUBmPo1eljrzcxvEmpI7jlnpc/3k/5u39Rqktz0sJ2fqymVU6RQCgFAKAUAoBQCgFAKAUAoBQCgFAdTvn/ANEw/kn1ms6/ZmvBv8wfkyscLtW2vW1umLZaHOYrA8xtXLC2ZX2Pq8b0nV59FfNbS25O9IeF8Ot2s2HvMbkiFFw3A3fMzGmsyPfW9R0svs7ng8L+0usLps2TW+b8vG5BcKnr7Mb9YkeeYRWEVeStzPfxklHD1HLbK/wJTp3/AG+/+h/lpV63vv8AXccfA/4Cn6/7mRmDu4cA9dYa606EYh7cDuhdD5+NRCajurl8ZgatealCs4JLZfjujOcRgv8Ag3/529V+mX8q/Xocn2Rif+al8/8A6LT0zsInD8KtsFUzKVUsWjMjNGY6nfnV6/uR/XcefwPN12qpO7Sau++0kir9G+HpiMTbs3MwVs05TB0RiIPmKxpJOaTPc4rVnSwk503Zq2vqid6T9CBh7bXrFx2VdXR4JAMCVYAbcwZ0nXSD0VaUVG6PC4TxjETrxpVnmUtL96foVnhWKNq9buDdXU/HUe8aVyRdmmfT4qkqtGcH3pnZ+NYw2LFy6IJRS3aMAxyJr1D8xNX+lLeIw3W2mDKfHaDBnugijJRHYa6BYEka3Lka+VQSaHGsUDYVBHbQCS6IFjKZbMwMacpqUQR2A4xZw6hGuWmM5jlu5twJ2XXUGm4KZ01xSXsRnS4LkpHZDdmCYXtAHYz3a1ZbFZF+t9ILChVe4uZOWV100jQrOwqtiT5wPFWUcsLtplIg+sAyy8mQQPKgLBw+8r4iQc0MsMBI9kc9t6A0ugzS2/ImPePtqSO45p6Tscl7iN1rZDKFRMwIIJC6wRykx7jWctz08J2XxKrVTpFAKAUAoBQCgFAKAUAoBQCgFAKAUB1PEf7kw/kn1ms6/ZmvBv8AMH5Mp6qSYAknYaa/TA+muSKu7H2FetGjTlUltFXDoQSrAggkEHcEbg1MouLsyKFeFemqlN3TLf6OuF2rlxrzvL2z2LcQFkfdCZ7XcBpHjpHRh1HfvPmf2jrYiLVP/hv5tdz/ACIzpz/br36H+UlZVvff67j1+CfwNP1/3M0OH4XDupN6+9ppgBbWcERvPnyqIdHb2rlsc8eprqyjltrfn8Tb/o7A/wDG3f8Alv41f/B8TizcZ5Q/XqWLpnfR+H4U2yWTOFDEZSciMsxy1WrVmnCLWxycGpVKeOqxq+9a7t4tP8yr9G+ILh8TbvOGKrmkKATqjKIkjmaxpyyyTZ73EcNLE4aVKFru2/g0yf6T9NBftGzZRlDe0zwDAMwACd43natalfMrJHk8N4G8PVVWrJNrZL+pV+FYU3b9q0updwPdux9ygn3VlTjmkkevxDELD4edR8rLzex0f0ii5dsLYtCXdwTqQMqyTPf2o0Pnyr0j82sVnojhL9pbuH6pDcuMusABUQElmIGss4A5ntd1SwWSz0VLCL198on1dtiqakE6mWPwqLkm7h+jGDQyLCE97DMfjNRcEguCsoNLSCNoQaaeVAU7pjwO/iMQhW3aCWxNslipYtlLZgO5k8NDUpkNFywVklFN1EFwqM4USA0doA7xOlQSfb2AssDmtoQd5QaxtOlARWL6JYVtbYay3JrTFY92o+FTcWNS3gGwTZgS9lh1bnZ0D6Z+4wSCdtBRMho43xTBNZcI8ZsqkwZ3FUnuenhOzNOqnQKAUAoBQCgFAKAUAoBQCgFAKAUAoDqduzcu8JsWrVtnbIjaZRpmbmSBVakHOFkZ4HFwwuMdSpe2q0ID+hsTaIe7Ya2ontNctiNDGzzPlWUaLi020e1iuMUcVQnSpRk5NciGv3GV0OrdYmY6icwJB08orarTVRXjujy+GcQnw9uFeLUJa7a38L29fQlsFisRgrlq+bTgNsJU51O8hWJAPeRvFYxoyhK918T1MTxPC4yjKnkm1zUb2fdsYeLcWbF37l4WXXNGmmmVQo1MTMT76mpSzSumviV4bxGOGw0aU6c7xv8A6Xbds2G6PYwDMcM4XvNy0B9PWVTq8vA6o/tBhpPKoyv5f1PNngWLcwuHLHuW7ZP1XKKg3s18S0+O0IK8oTXnH+pZuMcNvjhuFtG0RcW4xZC9tSPunMuFO42J3rSVJ5FG60PKwvEqfXqtdRk4yXcrvu3+BV/6HxMT1On56x/5ay6F818T1/tql93P/wBTcwHRTGXvZtogmMz3UI/wy5q8cO33o5a/7RQp6Rpyv/1afV/Im+izWMFdxCuwa8ikLdbsgwYKIusSRO5J91dEIwhomfP4uvjMY884u3cknZfrmZcVxrD3XLNiLczP3VdIGnzCQNe/nWh5uht4fi1pYuJdRoJB9YvagGQTlHn9FAb9jpClxtLlkKeZuiTpyA8e/wAagHw4tSYbGLMaquUfWSRQEXjON4bISbl9xmjcIGInTPAESdgZ0GlTYFeHHb9xsyG4qncBhOs7Z1127lFSQTfCekNvsrd6wMOzKsdIA+Y3a/UL1Fhcm73H8PbAK3nuSYhSrEf3gQCO7zqLEmV+NAQRetwY7LaHXloT9VAQ3FuL9d6sMqgEEkNmU+8RtO1WRBzjpeB8qaDm7K6/TWctz08L2fqyFqp0CgFAKAUAoBQCgFAKAUAoBQCgFAKAvnC+lV3C4aw+SbQHVakCTrECJyyCJkGY5VpFaHlV+0kY+OdI3xa25gKJaB3nTXyA+NceId5ZeR9b+zuGyUXXe8tvJfV/giGd4GcAEr2gTy01I8Y+qmHllnZ95rx7DKvhekjq4a+nf9TzYxRuy7HMZjXcREDYQI1A7jVsVujn/ZnsanmvwMQxc3DbCkkamNYEAyfDXeqdC8me53vjFNYvquV3ulfS2quWbhPEX+TYqwWJTqw6gn2SLiAx4HNt4VSLeVruLYvDU1iqNZK0s1n4+y/oR/BuIthryXU3U6j8IHcHzHxiqxlld0deMw0cTRlSl3/J9zN/pbxz5XekT1aaID8WPifqAq1WeeV+45eFYDqdGz956v8AJehs8M4J8o4fcdBNy1dLKB85ciZ184EjxAHOr06eem14/kcPEMc8JxCnJ+642l5Xevp9eZp8B6QPhkuKh0cBl0mGHMea8/AVWnUcLo7OIcNhjJU5cnr4x3/t5kKxLNHtE9ozJnXnBB1PiOdXw9O7u+45uO47q9HoYe9P5R7/AI7L1N9MKUWXyLLQAEuMWI5gF9pIHvruPiLDFYNUyG5lhtcwDjkYEMx7o5UFj7bwmxf1aZoGaR7XPICW1AB7UDQa1INrhNgERh1Lk6Fmy9gg66dpdvwixJO+lQLFjvcBQgNdLXGBJVc0KPBDqRPgQNNqgmx9sWB7IGUEeysHTtc9zoKgHq5wGzcB5nYxBAPj7oqbixC8R6OXEErLqBA1JI8m0eI5AxU3IsVu/iHUxLqJlleWgT37fSBUoqyPsYi8hlMqyCMwA1gTE68wNqkGDibXDcPWmXgToB5DSsZbnq4TsvialVOgUAoBQCgFAKAUAoBQCgFAKAUAoBQEvi7pOEtYZhq7h7bA6ZJYtPMESRHMRHOtL5Y35HnOjKtiOijvJ2M7hQsE5REDWOXL3V5ybcsx+hSpU4UOhvljbLy7rCxlygKcwGm4P00k25ZthhqVOFFUYyzRSt3PT08DDgLZXMp2DHL4Awf31rXnmyvwPL4LhnhnXpPulp5W0+RIXsJcRUdlhLgJQzIbKYPkQeRrJxainzPSpYunUrzor3oW9VzX4E7wfCW/kGLu5812FQrEZFzqR55o38I5GdY5eidtzysTKv8AadGM/c1y/DW/j+Ro8I4M2ItX2STctBWVR84HNmWO+BI8RHOqUoZ00dXEse8JUpSfuttPy019DyeEFcGMU33xwtsd6wxL+8jTwE86mVPLC73ZXD8RWIxzpU3eEYvXm7r5LZepdPRm0Ye5+d/7FrXDe6/M8P8AaT+Ih/2/myqdM+HJYxThPZYdYB+DmJkDwkEjumOVZV0lM9zgNWVTCLN/pbS8lsbg4VZtWQflDJcdM7hEV2hgDBBByrsJ023rspK0VY+Q4lVlVxVSUns2vRaIp+KxrmFF1mgyFAXT9IAAHTYE1rY4Cw8P4dfuZTl6rQgMxLNrGzHtDTTswD9UNliyYLglm32ri9Y0au+uu2xqCbEnw9lUQYbUxlX2QffO/dUAcbCFAQBEkGP7p+g+NAzBhJ6vQ5oXNJIJMrBJn30II3hWIa0cpNssSDkUEDUEt745+FSEWtyOrLZdlka+HhNQSVm5g7OLHrUGYfOEiP7rDX+NSQV7H9DWSepfMOYaJPwg++puRYp/F7DJdKOIYAaa1nLc9PC9n8TSqp0CgFAKAUAoBQCgFAKAUAoBQCgFAKAmOD2LbMTddl7CqjKCSNsw9kjlE+dXaTjrscNOpVhir0ffbstE9/M38KwtXCyk3ViALir4a6L3iuTplH3FY+plwitiYLrdZtruSVl8tTexN+xeAz5rDLztqDmnkRlJ+GmutaRqRqaSWpw1+H4nhydTDVPZdr6K/hunzI7Dpb0F65dVRPaUKx1iBAtnu+JqlNxnLLl/E6+IwxWEoutGu29F7sfob2F40ThDhbi9Yq3GNu5OR1EyCAV8TuOZFXrSUPZS0OPheEq4xvFuq1O9rpLkvT5E9f4FhsLhute/iPX2guQG3JzZX09WNo3Pf3xUy6OMbtb+ZlRqcQxWJdKNTs29Wo6Wur7bvkRfRvjTYJndEZ0eF7bDQrJgFVGsNrp3VjGpl1jFHp4nhvWZKjVrtyir7RWj07kuXMuHFL1niOBd1Z06kG4VUqGBRGIUypEHvA+yt88ZwbtseHHDYnAYyNNSs52WZJO6b8SB6IcUNuxibduRlRr4ZyGMqFGWAqiNPOs6dXR2Vu89LifDZOdKVWq5OUlDZKyfkV3jOPuYp+suMQ2UL2MoGhJ2Knv76zlVUndx/E9HD8Kq4eOSlXaW/uxf43MeIxbMsFmMAAKIA7IiQYEGN43k+VdFKum1G1jxeJcDq04yrxnm73pZ+L5DAcYSw2a3YTNzY6t9M/VXSz50lV6aXp7NlNOf0+NRYXMj9LsQxHqU15SSDrv4UshcHpZf2FhdN5LD3aHb40sLsw3ukF86G2As7CCJjXeT++lkLnhOkt+3JFoajUFYBknuHnTQXMK8XxB7QszBkZoMEbRI5d5mg1N89JcXEG2ukTAB950pZC7NTEdJ8VIKqA0QdBr3DaliLn210uxQ9pFYbTlM1Ngmyscdxj3rxuXAAxA0G2kxWU9z1ML2ZH1U6BQCgFAKAUAoBQCgFAKAUAoBQCgFAZOEqOvJnWDAjy/dSv2Rbg6i+Ja8nbzt9Db41PZ7RA8ATrpvFZ4VR1vudv7SVK8XTytqOu11r42+R5OmXrS0GMvZMct+4+etbRVPXLueRiKmOkqfWM2XS19n5+PnqSOKyZTnjLznauCGa/s7n3GMjQlSaxFsmm+i8DzhSmX1eXLPzYidP4VNRzv7RXAxwsYWw1st+531MwxnWgKXcpbYrAOq69oKWBAnyitKrs43V9DzeGU89Ouqcssuklro/LR9x0K5wDDf0cBnvZQPlWbsdbqux7OWI025Vu4wybab2Pno4nF9cv0ntN5M1tN7ctu8rnRFyFxigkqcLdOsE6DsyQANmPIVz03fNbkfScRp5erqcs0lUjrovPRehj6MTlxcR/Zbm55aTVae0vJm3Fd6H/kiQZto3tqTBBENGo5HvB5iopzyO9jbiGCeLgoqbjZ30/uj78oFtlIAHaBA1IEGfExV6cXUndeZz42vDBYPJOTbacVfdu36/uTdrpGuaTkWTr6lvtrvsfA3N7/aW1oeuQRyNi5sPKaWJuB0rtlwHupA+cLLwP30sRmNi50ttD78keFi59lRYm5gXpyp+/W/+XuDSft0qcpFz6vS2yw7V+3+xu/ZSxNzXHTBV2uIYgaWrn0ajnFLC5mtdMLTpFy6i67dQ5mPIHwpYXNA9IrQn11sjlls3f3r40sQ2fD0ltgyLgMaiLRHOATNTYgq3SHFm7fZyQdANBA0/nespbnqYXsyNqp0CgFAKAUAoBQCgFAKAUAoBQCgFAKA3LOCeA6qe+Qn7610cbPY87NVjic9K+ZO6srm8t9x7Vt/MDT65/neuKVCz9mSPraHG1KP+NSmn4RbX1Pl1braC26jmCup7x3D+dq1pUoxd21c8/iPFatePR0qclG6u2tX4L+4xC3HUjqbg5yVBG/OCailTySu2i/FOJLFYd0oUpptrePJ+Z4sl7aD1VxgdZVAB8SO6prU88rpoz4Tj+p0XTnTm3e+kfBeRjspfDE5BBlojKYJ0B8fp51ecISik3qjjwmMxGGxE6kKcnGbbas+d/Rq/wCtyTw2KvAgol0ErlGq+ydMurRljl8Kw6KWa+ZfE9n7QwnV+j6GeXll/O+/je5fuB8FSxg8R6y3cv3rLCFuLA7DZUUsRuTqxjlsBWsYRjFxT3PHxGNr18VCtUg1GDVkl43fLVkH0f4fetLiust5c2GdF9dZOZjEL2bhie8wPGs40rJ6rVHpY3ika7pZac/ZmpO67ly13K/gLdu51qX1uWnCzaYpmHWKdF7JO4kSdNatTp5W7tWZlxLiU66h0FOalF31j4eDf9j4MJdzZWskiYJz248xLz47VEKbhK6kjXF8QpYvDunUpTT8I7Pw12/InR0bEd1ddz5Oxr2eiNy47ZMoAWDMjflv4TS5Fj7gui2gkfV3+dLiwxXRoAHQgUzCxD9J+jNzC4dLzlYYhRBMyQx29311KZDVinxVipL9G+GtiLvVrAaM0kkREcx5ioZKLTheixUsHAJnUqSR7iarctYyYno2I9nl3UuRY18L0VuFM+UZdSTmM6d425VNwkV7jeG6u6V8AfprKe56mF7M0KqdAoBQCgFAKAUAoBQCgFAKAUAoBQCgLRhL9z5OihAwgZY1J15gwI99KkHONkUwOLp4bFynUvazWm+pLYm5cuXrNwYJ0RCuYL1csFYc8w+aAI2EeNYujJtPQ9KlxihClOGaTcr2bW11589Tbv424+OfFNhbwR1YMoa2WGeyUYg5gDqSat0Tc3Ln9DKPFKEMGsOm7pqztppK/PkR3D7t23h8RZ6i9N7q8pBSOwWJDdvnmqqoSUWudjorcaw1SvSqa+xmvpzS2MmKxV1sFaw3ye9mt3GcmUynNm0jNOkgjxZ6OjJwUeRWnxjDRxc6+tpJLbXS3j+rI3+KXLtx8JcXB3wLFu2hJa2cwtwQRD6TqffUyot5fC3yMqHFaEIVoyb/AMRya02v6+R54hxlxjvlzYa9btqBIBSRFsJK9vv1FWdOTqZ/1sUhxLDxwLw123ztp71+Z46PcfZcXexi4a61u61yACkjPdDEasNgCO73VEKUozcudxieI4erhIUE3eNtbclbmR3R/j3U2cXaNi6xuW8sjKAsB1OaTqO3OnNR5iIUJRi1zRti+LYavVpTTayO+3inpr4W9TBhekoOEOCW1cNx74KnSIOUZNTuXUHup0E8mXxJlxfCvGLEe1ZRta3fz35MkrmDxJw62fkLhg055tSd5HtaaBdfA99R0MsttC64zh1XdXNOzVrW/r56FSVbq3BIciZgkwZ+Fdp8kdg6NQtq3Mdq0h159mqsuiB6Y4eOq/N3fpm1H76Ihmj0ew4OIOnzH592WpZCRm9JljJgbQzaDEKZIJ+93AKhbiWxzAnYBx+oauZlw9FCKcY5JBi0Y0/KSokWiWzpwmVEPI3d9vvbVEdy7K5wETiLQmSX/Cn72x286llS9YN0W2y/OMg6HmNPgaqWOTdLxGNvjuaB4dkVSW56WG7NEPVTcUAoBQCgFAKAUAoBQCgFAKAUAoBQF34DgZs226xxK7dmPD5pPxrRbHlV+0kTDrcAJF1tATtb5D83UmZjF25t1rEd0Jr/AIdAfFRhp1tz/D/8dQDyA7KD1tzYE6W/f97oCx30uGxGYMptg9zCVjQjQ/QKArd3AHfrrkc5ufw0oDVvWtoxFz9oI+qpINHE4cgfdWjn2pP0ATvUg0OEspxNgBpYXE18c4NGDrhLHLqQfLNyNULGQs3s9Zr3ZP4VIMNlWLmTmGXmCI8tBQGaxnA9sgcvV7e+KAx4ouV0uGNdk3/+NAVT0qa4K3rPrlk/oPUx3InscpZNeW37q0Mi7+iRVGJuFoPqoH6y1WRaJ02HLtDECdBkzRp35D9dVLmG6HIkXPot/D2KAx4RPVGTLbzB090eFAct9IAPy1pMnImsRy8hVJbnpYXsyuVU3FAKAUAoBQCgFAKAUAoBQCgFAKAUBY8JehMOqm0A2jliZHcI8Y32+utVseTX7Rm/g+IJcZR1WVWznMz6QhAJjbWfKhmSSvh9s9o/pD7aakmZFw0CWUHmC4Gv06VAPjjDwfWJ+1/+1AWXqh8nlHMC2JAYMD2PfHuigK5xYzYuDll8PjpUogqWM0tWNBox0jvYfZUgy4QDrb8nSWk/p/uoDxw0g42wAdrib/3x5UIR1fE5yBkMaifIyPdVS5XcRxKwrG22JthwxB7DZgQYInzHlU2IJ/hhdS4Zs2wE9wHf5yagGnjr5QZrt1UXrMq5gYMiQNDvofOPOgNbB4sXM5w9+28ZQQmwzExoT3A/GpBq+lBP/wCNPzq8/wAl/tqY7iWxypbe+o+mrmZePRVaXr7s/ih/1CqyJhuXfi19lzlrq27S5YLaDtaQx8/rqC7I7C4pXY9RftsQMxW20zHfJPM/yakgkrBfq20GYg67gGNPdNAcw6eZvlZL7m2h8pG1ZS3PTwvZleqpuKAUAoBQCgFAKAUAoBQCgFAKAUAoDebGtbW0yhjup/BbXbf2hIOm891ax2PJr9oyRt4tUuAFMtzrIENvnmcsDUHRT/IqTG5Ncbw4uIEDEy3aVWClhsZO4AmoRYxX8U2cBXRVC5ssjMYBKAEwpBClSogg+BFSCRVkCiSCAoOblG0/CPCDUEmf/a7B3MlhAHbJBuQAEKoTudWOnKRSzIuY7pRwyZlJjUA6we/eoJNW7wy3AHIHTQafCpINY4RQSwIkzJPOdTMDXWlwRvDI+V2DuRcQyBpGYVJB1ZbyyASI0GsDnVSxyPjv9tvfnn/66sVOwrBd9j8fH99VLla6fQcPZiDOKQaeCP8AbUohkB6PZFjFsNDNiDpprcHPwNSyESHTq+z4BczZvW6kwIAVuYAHP40W4Zz3ChA6AjNmYAiYEbtJ5ad3/wC2Kl59HeE6rE4m3mByjLm5EB9/hUMmJOekL+w3j+VaH+J/CoRMir+jIDrb8/iu/wDLBqzKxL5buaco2PvqCxzT0iLGMI/9q39VZS3PSwvZlZqp0CgFAKAUAoBQCgFAKAUAoBQCgFAKAn8Fiilu2CqW29pbkasrFdJ5GQTB7vCtVseTX7RmTjfCgmIzW1DBYDSTBYdrYQdVYGPPu0m+hlYyXs4urfu57ioqu6KVHVFwd9SDIO58RQkhxh3uvnLMEbfICSCD3ab5iNDUkG5dsMuIIutktg9oZTDRtm1M9mF56LrQGLhSrbs3erAu5gyMVEsobY7AgdnlpJGs1D1CJHHvPXPhesD3mt5GGUK8QrbAZTJOu8zQB1uAXEW80Cym6kMr5u2o1MkqDDa7j3iT62NRbbC3dzMigRdOXVYDdqYMkzQGO1grwsWsYiCVIZhkMEh/aSdCBpPlzqSD1wHEbXMS9x7puK4GaA/V5uzm2EFlIHLwowecdb6zE3IjL15KsVyEoQWYkNElTpvprpQF+4RxdLhObtOVtklO0sujaiNh6tt6rYsR9rHWMTZXOGOV86qVOmUe1pI+dt4CgPXDbGGs2bttNHdbeZe12shkkSNu0aEGXE2utt2ltFAyv1hUmNFgggH2oYDQTQFA46t/CYss6IczG4FgFSPaI1ErAYGNCJFXRV6Fn4A1ux1ly1ni8k2jkzlZCsqhQZJGYgz3CoLGrxi1iwDZxLXGR1FzKVAMqwWDz3Omu2uxECD1wfAthXcLctB2XIQt0NIkTOpCkHUkmIPKDUkI2bPHrqgoCgGbqwGI7TRmgE7jT2x2dN4qLE3Kr0rxTXcRnbLJRIysrAgCAZXSsp7np4XsyHqp0CgFAKAUAoBQCgFAKAUAoBQCgFAKA2MJxTJNsdo6QCdFIPtL48q2S0PJr9ozebj1ubvXK2e6LYZlMdXkiHUDQsPtGgNLGRiwfGUw9y5mU3HYG2zM0rE66D2pIEGdBtU2uRc9WVDM1xHt5NWLO7AnYlCsSzLOwEc5iKEnnpPxAMSyBVZ/bKse0F0EjWPZ5k+6iQbPnRXjdqwxN1C4IiA2WPGYoyEyfGOt20t3MItu2bm/WXg3zlzEAklc0lYgkwNI3ixY0rXFrV0tbuLMF2yLeVETKAFyh1Bb3NmMwBQg2sDxi1deLltEJtwXNxT2kEwoGgBEDqyQDJJJ1oSRPSbjD3Fe31ysobdRo/MqdZGUyBpB7xoKlEMhMOUcqr3WS3oGgFtNJIUQJgVJBd8P8nc4Bc1x4NwWiLcC7FxNLqyTziZiVnaoJJ/hptm0L+HturO9wC4wUXIi4ZMaZcyqAPLxmCSI4hxW9ba/Yt5GuCZYoM7ILfanUSMqA7b/AEUBvPir/wAi64sOtGGzFgRovWAGCBr6uKAw8TxV/wCQYMzLZs2g5BgbYOkDTLr9uoX0Kpx/j74zEW3uAKpd9C2g63Lm1juAqxRu5p4nEhGtnbIFGgHay20gnXUZhHkT30sTcl+JXGu+tvArcZV3BAyHKUCztrJ3JkmiBFcJ40cLies0YDTbPHsnQEgHVRuRpSxA4hxtbmHKAwzOHKqpCqYAMT4CNDzqRcj7NwsozEnlqZ0nasZ7nqYTsl6nuqHSKAUAoBQCgFAKAUAoBQCgFAKAUAoCRTj/AKn5M4AWfbVBn3mCdJE957u6tYrQ8mu/8SRqnFWhCskjUhsokydcwaQdZ5++rGNzVxGOKkFMsDQdnTwhTMeW1TYg8txFmaYQNpBCKP3c/opYkxYldAw1nWI2BH0byKBmpkPcakqFPKgMr3QxzGJPf38586Enq8Mhyq2YaE+B/n66AyvJGUtmY7AAzI2DSBryG5NQSa2UjcfTpUlSew/HcRaNnMkdUGFpipBTPIbKdjqOc7VFi1zHd49eTKqsygAhlV2CmdTAnTv076WDZd+iOGbFxiOsBuIjIwMyRc5mJ3gjbvqr0JWpOngV4WBYzJlFoWRKtMDJqY/ufGouSY8ZwO69tLUqoQIogMZyEROgPzRS4sc/9IFnqntYfKoyWw0rPazKqaz+Zn9I1aJWRv4bofexeHW6nVjMQRJIIVM6R7Ox7J3+aPcvYWueV6J4pD2ijQuQDOZHPmAI0POpuLHwdB7lwLBVHJJfM+m5iNDygGAaXFjCfR3ih8+wdPwnHL+537UuRlInHcLuYV+quZcwAPZMjtbbgVlPc9XCdkvU16odAoBQCgFAKAUAoBQCgFAKAUAoBQCgMN7DNlZyDlDLB8wwPxj4VvF6Hj4jtJH25aLW5G6ifdzqTE1BqpHPT+fjUg92cK0zBEa7eX7jQlEljL9y8LanKMiBVVQFEAbgTBJzAk8zUEmWxgLkpkQxBDSfnEfVJkVAIvGYf110LsrPHkpMfAVYixhFowXA0B15/wAj7aCxt4q42JcNlUnKAQrEkhdADJJmBvUbE2uWG10Sxl+4b+QKN+0YMgaSNeYGvvqLk2LDa9HyzkxGI9lOQEDUNk1PjPLnUZibFM6Z2guJyK+dEQKGknbNmEknnPOrIqzFwbhz4z1KDtAyGykjXKCGjYTBDeJpsRudT6G8Bu4MFS4OaJUAOpYCMwlVZdANMxFVbuXSsWZnYT2VP6Ef91VJNZmgyVH6v8akHLun3Dr17GF1tsVKIAQukiZG3jVkykkX/o6/VYWyhtlGt21RgX1kASeypG+tV7yyNzE+tI9W0jUnO3ZkH8Iba8qlAjMdmt+0sg8wfqmKAWeJMo0kg8iZ+NSChdOL4fFswBHYUQfKspbnp4XsyAqpuKAUAoBQCgFAKAUAoBQCgFAKAUAoCx4LG3jZW2trrFCkQbRYGZHa761Wx5NftJGHhPAMUEdWtXVDj5pQRuDoWBIgxU3MUmTGB6D5R2nIB3WFPukgx7qOROU316J2UghQYPPX4THwqLk2PD8BvjVFA159nSI/nSgsaNzo1iXb2wPIMR4napugeH6A3Wdm6wAtuArRtHPyqcxGU3uA+je7aYObtsxuHslh7u0pH01DkTY6NY4PZUfcrf7MfvqpJ4xPDLUfcrf6g+ygK5jujC3mkqqD8lQv06a0QNdfR/hjG8ifnEbnwIq1yLG9guhWCswVtDMNjmefg2u3OouTZEv/AEfbX72v0kVAPIwSHTqx+saAXOH249kD9I/z4++hItYRRsung38JoQfMRhEEQD+ueWnf4VIPItCN28w5+OtAemwIdSJYg6EFyY+FECG4hwQr2kG3LSdtv5/jUkM5t0oEYhpEaCs5bnpYXsyJqp0CgFAKAUAoBQCgFAKAUAoBQCgFAKAsnDcfdW0gVyABoBXNOpNSaTPoMLwzCVaMZzpptrXf6m7a4neJC9aQCQJMQJO50qnSz5m8uE4JJvovm/qW3E8Bu27aXf6QslbjZUIU9uGCnKY1jfxA0rZqaV8+54sJYOU3DqrvHfV6aX11NnF9G8ZYW4xxqgW3RGPVsPuhQAg5dR2+XcalwqrefyKUq2AqOKjh90373K/j4Gj0m4fisIjF8crurKptgEN2hIYSNR4iRuOVVmqkFrI6MDDA4uaSw9k03e7a08mZDwnGJg1xbYwIrJ1gXKx0MQCwEBjI076m1TJnciqeAliXh40LtO179/lfbxN+30XxxvPZXHLnW2tz2WAIcsBy/J+NW6Ore2Y53ieHKmqjw7s21vyt4+JhscF4izWV+V5TcR3cMD6oWyFcHTU5mjTu7qhRrae1v8jSVXhqU5dDdRaS19692u/TRXMeG4dirrstviSOosi/mWT2Z1BAEqRpoddahKo9p91y03g6cE54Vp5strvfzvqZrPR3iDrh3XGSl8A5oPYzIWXMI2MRPfHfUqFV2aluUlW4bB1Iyoe1DuvvrZ219TFZ4XjMivc4glkOzi1nMBwhIkkiFncA6xUJVLXc7F5SwObLDDOVrZrN6X7t9SP6LHGY3rcuLNvqlDnMpaRrMADlG25mqU3Une0tjqx+HwOEyXo3zO27X4skbXCeIHFvhflagpbFw3I7MMQAp7MhiTse6r5aubLmOWU+HLDKv0G7ta7vp377HnhfDcbeu3bBxyJdtOyFCslgsdsAD2TNIqo2459UTiHgKVOFVYduMkne7sm+7fc+8O4bfvFxb4nZbIC5yrPZCqS2g0Azx5g0ipy2mitXqlJRc8JJX01bWuum/hcx8K4NjMUb3V4xGW22RXABF05SxCachSCqSvaWxbES4fh1DPh2nJXau7xV7a6mhdfFpgVxhxcBnNsW8nazAsCJyxspb4b1RyqKGfMdUcNgZYt4ZUdle99LWXj42Jg8Ex2cD5YhVrPyh36vRE0jTLJJjYfgmtMtW/vd1zh6Xh2Rvq+ubKlfd/E92OjnEGutaGLTS2t1GyaOrkj8HQgjUHvFSoVb2zFZYjhsaan0He01fZr1ITjpxuESy9zEdq6GGQIAUyEBg3Zgwxis5urBK8tz0MHh+H4qc4wo6Rtrd6327yG/2kxX45voX7Kz6afM7/sfBfdr4v6lY47iWuXi7nMxAkwBy8K6acm43Z4eOoU6FZwpqy0I+rnGKAUAoBQCgFAKAUAoBQCgFAKAUAoCcwX3NfKuKp7zPr8B/DQ8jNVDrLBiOkufD4Wx1KhcM4cHO0vzYHuzHXTblWjqXjFW2PMhw7LWq1c7vUTWy05fD5krj/SC15bivh1IuOjn1r6dWUIAHIdjlG5rSWIbvdb+Jx0uAqm4uNR6Jr3V33+po9Jel/yxGU4dEZmVi4YseyIAEjQRyGkydyarUrZ1sdGB4V1WakqjaSatZLfy39TJhumht4M4VLCANb6tmztBBkMcmwYyZYc/IUVZqGWxWfB1PE9PKo9HdKy9FfkuRnxvT57husLCo1y0trMLjSmQsVYeILT7ql1276bmdLgcYKEXNtRk5Wstb2uvke7vpGvtdtXTaQlLbWnEmLgfKWP5JlJ0mpeIldOxC4BRjTlTUnq014Wv8dz6fSE+efk65RZ6hVN1jCn2jO5JgCd+zTrDvt3WI+wY5bdI75szdlv3fn8Txw/0hXbLWillQqWVslM7QwT2W8CNf1j4VEcQ42su6xNXgNOqpZpu8pOV7LS+69fyHCvSFdsoqmyjsmcW2zsuUXDJUgaNqB9ApHENLYYjgNOrJtTaTtdWTu13+BFdGekhwZvHqxdN5crEuykDXNBGsmd9xFUp1Mjel7nbj+HLFKCzZcjutE/xJcekN+su3Pk9sNcFsSHYEC2SQCeZJJk90DlWnWHdu25wvgMckYdI7Rv3LdmvZ6bFca+NGHTO9vIVztHIFvMhQKqqzU3OxrLg+bCxwzqO0Xe9l8CO6N9IBg3vMtlX61DbguwyqTJAPPlqddPGq06mRvTc6cdgHioQi5tZXfZavmSHR3ps2DspaSwpyu1wnOwzlgR2h4AgfoirU6zgrJHNjeDrFVXUlN6pLZaW/XzPrdM1Nk2Wwdpk6y5dUF2IVrhfWIjQPA8p3qemVrOKIXCJKp0kazTslolsrfjYynp++dT1CZBZ+Tumdu2nLXcEa6/lHwqesO+3dYr9hRyNdI75sydlo/zv+R4xHT265unqlUPZFm3ldgbQWSCDzaSDOnsiodd66eHkTDgdOKh7TdpOTul7V7aeC+pH9KulNzHiz1iKrWlIlT7RbLJjl7O3jValV1LX7jq4fw2GCc8jupW9LX+pAVkekQ/E/uh8hXZR90+W4r/EvyRq1oecKAUAoBQCgFAKA//Z</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273de95344a3bafbaed194ea4be</t>
+  </si>
+  <si>
+    <t>https://f4.bcbits.com/img/a1925398695_10.jpg</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d00001e02f493feb1f55bb2f4fc2fc312</t>
+  </si>
+  <si>
+    <t>https://cdn-images.dzcdn.net/images/cover/f04f288a84967d273e768d185a7b8303/0x1900-000000-80-0-0.jpg</t>
+  </si>
+  <si>
+    <t>Descripción sinóptica del episodio</t>
+  </si>
+  <si>
+    <t>Un niño desaparece de 1983 Hawkins, Indiana, enviando a sus amigos, familiares y la policía local a una búsqueda frenética, una que lleva a una chica misteriosa y una serie de pistas inquietantes.</t>
+  </si>
+  <si>
+    <t>Mientras Will sigue desaparecido, Mike y sus amigos refugian a una chica misteriosa, mientras Joyce cree que su hijo está tratando de comunicarse y Hopper investiga una serie de extraños incidentes.</t>
+  </si>
+  <si>
+    <t>La caza de Will se intensifica ya que Joyce cree que puede estar tratando de contactarla. Hopper sigue pistas inquietantes, y los chicos cobijan a una chica misteriosa que podría estar relacionada con la desaparición de su amigo.</t>
+  </si>
+  <si>
+    <t>Un descubrimiento preocupante intensifica la búsqueda de Will mientras Hopper sonda Hawkins Lab, Joyce sigue señales inquietantes y los niños albergan a una chica misteriosa que puede tener pistas cruciales sobre su amiga desaparecida.</t>
+  </si>
+  <si>
+    <t>En busca de respuestas sobre Will, los chicos recurren al señor Clarke; Hopper y Joyce persiguen una peligrosa pista en Hawkins Lab; y Nancy se une a Jonathan para investigar la desaparición de Barb.</t>
+  </si>
+  <si>
+    <t>Hopper presiona Hawkins Lab para obtener respuestas mientras los chicos reclutan a Once en un atrevido experimento de privación sensorial para encontrar a Will. En tanto, Nancy y Jonathan se arman y le ponen una trampa a la criatura.</t>
+  </si>
+  <si>
+    <t>Mientras la ciudad se prepara para Halloween, un rival de alto puntaje sacude las cosas en la sala de juegos, y un escéptico Hopper inspecciona un campo de calabazas en descomposición.</t>
+  </si>
+  <si>
+    <t>La conexión de Will con un mal sombrío se hace más fuerte, pero nadie está seguro de cómo detenerlo. En otros lugares, Dustin y Steve forjan un vínculo poco probable.</t>
+  </si>
+  <si>
+    <t>Las visiones psíquicas atraen a Once a una banda de marginados violentos y a una chica enojada con un pasado sombrío.</t>
+  </si>
+  <si>
+    <t>Nancy y Jonathan intercambian teorías de conspiración con un nuevo aliado mientras Once busca de alguien de su pasado. “Bob el Cerebro” aborda un problema difícil.</t>
+  </si>
+  <si>
+    <t>Un testamento enfermo se abre a Joyce, con resultados inquietantes. Mientras Hopper cava en busca de la verdad, Once destierra un descubrimiento sorprendente.</t>
+  </si>
+  <si>
+    <t>Dustin adopta una extraña nueva mascota, y Once se impacienta cada vez más. Un Bob bien intencionado insta a Will a hacer frente a sus miedos.</t>
+  </si>
+  <si>
+    <t>Después de que Will vea algo terrible en la noche de trucos o golosina, Mike se pregunta si Once sigue ahí fuera. Nancy lucha con la verdad sobre Barb.</t>
+  </si>
+  <si>
+    <t>Hopper y Joyce lanzan una misión de última hora para encontrar a Will mientras los niños y Once se preparan para una confrontación final, mientras que Hawkins Lab se cierra y el límite entre mundos se deshace.</t>
+  </si>
+  <si>
+    <t>Hopper y Joyce presionan Hawkins Lab para obtener respuestas mientras Nancy y Jonathan persiguen una nueva pista peligrosa. Con la búsqueda de Will escalando, los chicos luchan por mantener a Once a salvo e invisible.</t>
+  </si>
+  <si>
+    <t>Once hace planes para terminar lo que ella comenzó mientras los sobrevivientes suben el fuego a la monstruosa fuerza que tiene a Will como rehén.</t>
+  </si>
+  <si>
+    <t>“The Mind Flayer”</t>
+  </si>
+  <si>
+    <t>El verano trae nuevos empleos y un romance en ciernes. Pero el estado de ánimo cambia cuando la radio de Dustin recoge una emisión rusa, y Will siente que algo anda mal.</t>
+  </si>
+  <si>
+    <t>Con Once y Max buscando a Billy, Will declara un día sin chicas. Steve y Dustin van en un stakeout, y Joyce y Hopper regresan a Hawkins Lab.</t>
+  </si>
+  <si>
+    <t>Nancy y Jonathan siguen una pista, Steve y Robin se inscriben en una misión secreta, y Max y Once van de compras. Un Billy alborotado tiene visiones preocupantes.</t>
+  </si>
+  <si>
+    <t>Un código rojo vuelve a unir a la pandilla para enfrentar un mal terriblemente familiar. Karen insta a Nancy a seguir cavando, y Robin encuentra un mapa útil.</t>
+  </si>
+  <si>
+    <t>Extrañas sorpresas acechan dentro de una antigua granja y en las profundidades del centro comercial Starcourt. Mientras tanto, el Cazador Mental está recogiendo fuerza.</t>
+  </si>
+  <si>
+    <t>El doctor Alexei revela lo que los rusos han estado construyendo, y Once ve dónde ha estado Billy. Dustin y Erica escenifican un atrevido rescate.</t>
+  </si>
+  <si>
+    <t>El terror reina en el patio de comidas cuando el Mente Flayer viene a coleccionar. Pero abajo, en la oscuridad, el futuro del mundo está en juego.</t>
+  </si>
+  <si>
+    <t>Con el tiempo agotándose, y un asesino muy cerca, la tripulación de Hopper corre de regreso a Hawkins, donde Once y los niños se están preparando para la guerra.</t>
+  </si>
+  <si>
+    <t>Portada del capítulo</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTIhKcu6d_y4_aMVi35BCF4yuxV7DrOYCB9bzO4HhZBPQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSm9ZMio977_OSDEWqPLOi28kRr4BsNSbUeRLeZVzg_OIBNPd0WOMSo1zMf&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTf-3f2E6yGTgQmqhUFomYf-CnpBZLjWQdIix-kgqGUlQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT4t6KTWFtwGihnQ_33wPTfYm7znzcK9dd2XFPonibONw&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQWkfd3nSk4Vi5jvoj8d_kdWec8v8Tl-A3XP-NmYVf-Vg&amp;s=10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1183,6 +1641,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1205,13 +1676,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1551,13 +2024,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577478F0-FCB6-4E73-80B0-E68D9EB3C826}">
-  <dimension ref="B2:I164"/>
+  <dimension ref="B2:J152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1571,263 +2044,311 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
         <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>467</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E3">
         <v>1966</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="G3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>211</v>
+        <v>468</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>1967</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>322</v>
+      </c>
       <c r="G4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E5">
         <v>1967</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>323</v>
+      </c>
       <c r="G5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E6">
         <v>1970</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E7">
         <v>1967</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>325</v>
+      </c>
       <c r="G7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <v>1982</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="G8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E9">
         <v>2000</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="G9" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>469</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E10">
         <v>1984</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>328</v>
+      </c>
       <c r="G10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E11">
         <v>1982</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>329</v>
+      </c>
       <c r="G11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E12">
         <v>2008</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>330</v>
+      </c>
       <c r="G12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E13">
         <v>1970</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>331</v>
+      </c>
       <c r="G13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E14">
         <v>2013</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>332</v>
+      </c>
       <c r="G14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E15">
         <v>1969</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="G15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E16">
         <v>1978</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>334</v>
+      </c>
       <c r="G16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
@@ -1835,16 +2356,19 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E17">
         <v>1982</v>
       </c>
+      <c r="F17" s="2" t="s">
+        <v>335</v>
+      </c>
       <c r="G17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
@@ -1852,16 +2376,19 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E18">
         <v>1987</v>
       </c>
+      <c r="F18" s="2" t="s">
+        <v>336</v>
+      </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -1869,19 +2396,25 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E19">
         <v>1981</v>
       </c>
+      <c r="F19" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="G19" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>470</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
@@ -1889,16 +2422,19 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E20">
         <v>2015</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>338</v>
+      </c>
       <c r="G20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.35">
@@ -1906,16 +2442,19 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>2008</v>
       </c>
+      <c r="F21" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="G21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
@@ -1923,16 +2462,19 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>2010</v>
       </c>
+      <c r="F22" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="G22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.35">
@@ -1940,19 +2482,25 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="E23">
         <v>2010</v>
       </c>
+      <c r="F23" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="G23" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H23" t="s">
+        <v>471</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
@@ -1960,33 +2508,45 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E24">
         <v>1966</v>
       </c>
+      <c r="F24" s="2" t="s">
+        <v>342</v>
+      </c>
       <c r="G24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D25" t="s">
-        <v>167</v>
-      </c>
-      <c r="E25" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="E25">
+        <v>2015</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="G25" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H25" t="s">
+        <v>472</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
@@ -1994,19 +2554,19 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="E26">
-        <v>2015</v>
+        <v>1986</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="G26" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.35">
@@ -2014,50 +2574,65 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="E27">
-        <v>1986</v>
+        <v>1984</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="G27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D28" t="s">
-        <v>184</v>
-      </c>
-      <c r="E28" t="s">
-        <v>190</v>
+        <v>171</v>
+      </c>
+      <c r="E28">
+        <v>2024</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="G28" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H28" t="s">
+        <v>482</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E29">
-        <v>1984</v>
+        <v>1987</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="G29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.35">
@@ -2065,19 +2640,19 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E30">
-        <v>2024</v>
+        <v>1975</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="G30" t="s">
-        <v>8</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>170</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.35">
@@ -2085,175 +2660,217 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E31" t="s">
-        <v>191</v>
+        <v>114</v>
+      </c>
+      <c r="E31">
+        <v>1981</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="G31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E32">
-        <v>1987</v>
+        <v>1996</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>350</v>
       </c>
       <c r="G32" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
+        <v>473</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E33" t="s">
-        <v>167</v>
+        <v>114</v>
+      </c>
+      <c r="E33">
+        <v>2007</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H33" t="s">
+        <v>481</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D34" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E34">
-        <v>1975</v>
+        <v>1995</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="G34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
       <c r="E35">
-        <v>1981</v>
+        <v>1984</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="G35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
+        <v>191</v>
+      </c>
+      <c r="E36">
+        <v>1942</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G36" t="s">
         <v>7</v>
-      </c>
-      <c r="C36" t="s">
-        <v>192</v>
-      </c>
-      <c r="D36" t="s">
-        <v>193</v>
-      </c>
-      <c r="E36">
-        <v>1996</v>
-      </c>
-      <c r="G36" t="s">
-        <v>8</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>199</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>2007</v>
+        <v>1980</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="G37" t="s">
-        <v>8</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>195</v>
+        <v>9</v>
+      </c>
+      <c r="H37" t="s">
+        <v>474</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B38">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="E38">
-        <v>1995</v>
+        <v>1985</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="G38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>206</v>
+        <v>18</v>
       </c>
       <c r="E39">
-        <v>1984</v>
+        <v>1983</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="G39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B40">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>205</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="E40">
-        <v>1942</v>
+        <v>1984</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="G40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
@@ -2261,22 +2878,19 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E41">
-        <v>1980</v>
-      </c>
-      <c r="F41" t="s">
-        <v>343</v>
+        <v>1962</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="G41" t="s">
-        <v>10</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
@@ -2284,90 +2898,105 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E42">
-        <v>1985</v>
-      </c>
-      <c r="F42" t="s">
-        <v>344</v>
+        <v>2016</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="G42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E43">
-        <v>1983</v>
-      </c>
-      <c r="F43" t="s">
-        <v>345</v>
+        <v>1984</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="G43" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H43" t="s">
+        <v>480</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E44">
-        <v>1984</v>
+        <v>1980</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E45">
-        <v>1962</v>
+        <v>1986</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="G45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="E46">
-        <v>2016</v>
+        <v>1983</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>361</v>
       </c>
       <c r="G46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.35">
@@ -2375,19 +3004,19 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E47">
-        <v>1984</v>
+        <v>1983</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="G47" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.35">
@@ -2395,16 +3024,19 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E48">
-        <v>1980</v>
+        <v>1962</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="G48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.35">
@@ -2412,16 +3044,19 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E49">
-        <v>1986</v>
+        <v>1981</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="G49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.35">
@@ -2429,84 +3064,105 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E50">
-        <v>1983</v>
+        <v>2016</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="G50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>366</v>
       </c>
       <c r="E51">
-        <v>1983</v>
+        <v>1975</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>367</v>
       </c>
       <c r="G51" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H51" t="s">
+        <v>479</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>217</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E52">
-        <v>1962</v>
+        <v>1972</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>368</v>
       </c>
       <c r="G52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E53">
-        <v>1981</v>
+        <v>1984</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="G53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D54" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E54">
-        <v>2016</v>
+        <v>1984</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>370</v>
       </c>
       <c r="G54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.35">
@@ -2514,19 +3170,19 @@
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E55">
-        <v>1975</v>
+        <v>1982</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="G55" t="s">
-        <v>10</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>201</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.35">
@@ -2534,155 +3190,191 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D56" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E56">
-        <v>1972</v>
+        <v>1962</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="G56" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E57">
-        <v>1984</v>
+        <v>1988</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="G57" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H57" t="s">
+        <v>478</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E58">
-        <v>1984</v>
+        <v>1983</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="G58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E59">
-        <v>1982</v>
+        <v>2011</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>375</v>
       </c>
       <c r="G59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E60">
-        <v>1962</v>
+        <v>2011</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="G60" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H60" t="s">
+        <v>477</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="E61">
-        <v>1984</v>
+        <v>1992</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="G61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D62" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E62">
-        <v>1988</v>
+        <v>1966</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="G62" t="s">
-        <v>10</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>204</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E63">
-        <v>1983</v>
+        <v>1985</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="G63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D64" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E64">
-        <v>2011</v>
+        <v>1988</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="G64" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.35">
@@ -2690,19 +3382,19 @@
         <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D65" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E65">
-        <v>2011</v>
+        <v>1984</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>381</v>
       </c>
       <c r="G65" t="s">
-        <v>10</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>207</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.35">
@@ -2710,16 +3402,19 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D66" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E66">
-        <v>1992</v>
+        <v>2008</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="G66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.35">
@@ -2727,16 +3422,19 @@
         <v>5</v>
       </c>
       <c r="C67" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E67">
-        <v>1966</v>
+        <v>1982</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>383</v>
       </c>
       <c r="G67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.35">
@@ -2744,16 +3442,19 @@
         <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E68">
-        <v>1985</v>
+        <v>1944</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="G68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.35">
@@ -2761,345 +3462,423 @@
         <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E69">
-        <v>1988</v>
+        <v>1986</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="G69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D70" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E70">
         <v>1984</v>
       </c>
+      <c r="F70" s="2" t="s">
+        <v>386</v>
+      </c>
       <c r="G70" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H70" t="s">
+        <v>475</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D71" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E71">
-        <v>2008</v>
+        <v>1992</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>387</v>
       </c>
       <c r="G71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" t="s">
         <v>77</v>
       </c>
-      <c r="D72" t="s">
-        <v>78</v>
-      </c>
       <c r="E72">
-        <v>1982</v>
+        <v>1946</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="G72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E73">
-        <v>1944</v>
+        <v>1963</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="G73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E74">
-        <v>1986</v>
+        <v>1984</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="G74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E75">
         <v>1984</v>
       </c>
+      <c r="F75" s="2" t="s">
+        <v>391</v>
+      </c>
       <c r="G75" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H75" t="s">
+        <v>476</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D76" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E76">
-        <v>1992</v>
+        <v>1986</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>392</v>
       </c>
       <c r="G76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D77" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E77">
-        <v>1946</v>
+        <v>1981</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="G77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E78">
-        <v>1963</v>
+        <v>1976</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>394</v>
       </c>
       <c r="G78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D79" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E79">
-        <v>1984</v>
+        <v>1983</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>395</v>
       </c>
       <c r="G79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D80" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E80">
-        <v>1984</v>
+        <v>1962</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="G80" t="s">
-        <v>10</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>210</v>
+        <v>9</v>
+      </c>
+      <c r="H80" t="s">
+        <v>484</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B81">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D81" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E81">
-        <v>2015</v>
+        <v>1983</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="G81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B82">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D82" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E82">
-        <v>1986</v>
+        <v>1974</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>398</v>
       </c>
       <c r="G82" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H82" t="s">
+        <v>483</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B83">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D83" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E83">
-        <v>1981</v>
+        <v>1983</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="G83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B84">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D84" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E84">
-        <v>1976</v>
+        <v>1984</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>400</v>
       </c>
       <c r="G84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B85">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D85" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E85">
-        <v>1983</v>
+        <v>1957</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>401</v>
       </c>
       <c r="G85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B86">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D86" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E86">
-        <v>1962</v>
+        <v>1983</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>402</v>
       </c>
       <c r="G86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B87">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D87" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E87">
-        <v>1983</v>
+        <v>1981</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>403</v>
       </c>
       <c r="G87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B88">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D88" t="s">
-        <v>167</v>
-      </c>
-      <c r="E88" t="s">
-        <v>167</v>
+        <v>124</v>
+      </c>
+      <c r="E88">
+        <v>1983</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="G88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.35">
@@ -3107,756 +3886,913 @@
         <v>9</v>
       </c>
       <c r="C89" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D89" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E89">
-        <v>1974</v>
+        <v>1983</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>405</v>
       </c>
       <c r="G89" t="s">
-        <v>10</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>196</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B90">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="D90" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="E90">
-        <v>1983</v>
+        <v>1985</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="G90" t="s">
-        <v>10</v>
+        <v>193</v>
+      </c>
+      <c r="H90" t="s">
+        <v>485</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B91">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="D91" t="s">
-        <v>87</v>
+        <v>196</v>
       </c>
       <c r="E91">
-        <v>2017</v>
+        <v>1969</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="G91" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B92">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="D92" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="E92">
-        <v>1984</v>
+        <v>2005</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="G92" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B93">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="D93" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="E93">
-        <v>1957</v>
+        <v>1970</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>406</v>
       </c>
       <c r="G93" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B94">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="D94" t="s">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="E94">
         <v>1983</v>
       </c>
+      <c r="F94" s="2" t="s">
+        <v>407</v>
+      </c>
       <c r="G94" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B95">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="D95" t="s">
-        <v>130</v>
+        <v>408</v>
       </c>
       <c r="E95">
         <v>1981</v>
       </c>
+      <c r="F95" s="2" t="s">
+        <v>409</v>
+      </c>
       <c r="G95" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B96">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="E96">
-        <v>1983</v>
+        <v>1978</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>410</v>
       </c>
       <c r="G96" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B97">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="E97">
-        <v>1983</v>
+        <v>1982</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>411</v>
       </c>
       <c r="G97" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D98" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="E98">
-        <v>1985</v>
+        <v>1962</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>412</v>
       </c>
       <c r="G98" t="s">
-        <v>212</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D99" t="s">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="E99">
-        <v>1969</v>
+        <v>1978</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="G99" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D100" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E100">
-        <v>2005</v>
+        <v>1984</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>414</v>
       </c>
       <c r="G100" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D101" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E101">
-        <v>1970</v>
+        <v>1986</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="G101" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D102" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E102">
-        <v>1983</v>
+        <v>2011</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>416</v>
       </c>
       <c r="G102" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103" t="s">
         <v>222</v>
       </c>
       <c r="D103" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E103">
-        <v>1981</v>
+        <v>1982</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="G103" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+      <c r="H103" t="s">
+        <v>487</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E104">
-        <v>1978</v>
+        <v>1983</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="G104" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D105" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E105">
         <v>1983</v>
       </c>
+      <c r="F105" s="2" t="s">
+        <v>419</v>
+      </c>
       <c r="G105" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D106" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E106">
-        <v>1982</v>
+        <v>1984</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>420</v>
       </c>
       <c r="G106" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="D107" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E107">
-        <v>1962</v>
+        <v>2016</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="G107" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="D108" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E108">
-        <v>1978</v>
+        <v>1977</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="G108" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B109">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="D109" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E109">
         <v>1984</v>
       </c>
+      <c r="F109" s="2" t="s">
+        <v>423</v>
+      </c>
       <c r="G109" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+      <c r="H109" t="s">
+        <v>486</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J109" s="2"/>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D110" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E110">
-        <v>1986</v>
+        <v>2016</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="G110" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="D111" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="E111">
+        <v>1984</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G111" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B112">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>256</v>
+      </c>
+      <c r="D112" t="s">
+        <v>258</v>
+      </c>
+      <c r="E112">
+        <v>1982</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="G112" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B113">
+        <v>3</v>
+      </c>
+      <c r="C113" t="s">
+        <v>260</v>
+      </c>
+      <c r="D113" t="s">
+        <v>216</v>
+      </c>
+      <c r="E113">
         <v>2011</v>
       </c>
-      <c r="G111" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B112">
-        <v>2</v>
-      </c>
-      <c r="C112" t="s">
-        <v>237</v>
-      </c>
-      <c r="D112" t="s">
-        <v>167</v>
-      </c>
-      <c r="E112" t="s">
-        <v>167</v>
-      </c>
-      <c r="G112" t="s">
-        <v>212</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B113">
-        <v>2</v>
-      </c>
-      <c r="C113" t="s">
-        <v>242</v>
-      </c>
-      <c r="D113" t="s">
-        <v>244</v>
-      </c>
-      <c r="E113">
-        <v>1982</v>
+      <c r="F113" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="G113" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="D114" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="E114">
-        <v>1983</v>
+        <v>1984</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="G114" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D115" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="E115">
-        <v>1983</v>
+        <v>1985</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>429</v>
       </c>
       <c r="G115" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="116" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D116" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E116">
+        <v>2008</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="G116" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B117">
+        <v>3</v>
+      </c>
+      <c r="C117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D117" t="s">
+        <v>271</v>
+      </c>
+      <c r="E117">
         <v>1984</v>
       </c>
-      <c r="G116" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B117">
-        <v>2</v>
-      </c>
-      <c r="C117" t="s">
-        <v>261</v>
-      </c>
-      <c r="D117" t="s">
-        <v>262</v>
-      </c>
-      <c r="E117">
-        <v>2016</v>
+      <c r="F117" s="2" t="s">
+        <v>431</v>
       </c>
       <c r="G117" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D118" t="s">
-        <v>156</v>
+        <v>314</v>
       </c>
       <c r="E118">
-        <v>1977</v>
+        <v>1961</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>432</v>
       </c>
       <c r="G118" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B119">
         <v>3</v>
       </c>
       <c r="C119" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="D119" t="s">
+        <v>277</v>
+      </c>
+      <c r="E119">
+        <v>1971</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G119" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B120">
+        <v>4</v>
+      </c>
+      <c r="C120" t="s">
+        <v>227</v>
+      </c>
+      <c r="D120" t="s">
+        <v>251</v>
+      </c>
+      <c r="E120">
+        <v>1939</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G120" t="s">
+        <v>193</v>
+      </c>
+      <c r="H120" t="s">
+        <v>488</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B121">
+        <v>5</v>
+      </c>
+      <c r="C121" t="s">
+        <v>228</v>
+      </c>
+      <c r="D121" t="s">
+        <v>254</v>
+      </c>
+      <c r="E121">
+        <v>1998</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G121" t="s">
+        <v>193</v>
+      </c>
+      <c r="H121" t="s">
+        <v>489</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B122">
+        <v>5</v>
+      </c>
+      <c r="C122" t="s">
+        <v>229</v>
+      </c>
+      <c r="D122" t="s">
+        <v>255</v>
+      </c>
+      <c r="E122">
+        <v>1983</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G122" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="C123" t="s">
+        <v>231</v>
+      </c>
+      <c r="D123" t="s">
+        <v>257</v>
+      </c>
+      <c r="E123">
+        <v>1988</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="G123" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B124">
+        <v>5</v>
+      </c>
+      <c r="C124" t="s">
+        <v>232</v>
+      </c>
+      <c r="D124" t="s">
         <v>259</v>
       </c>
-      <c r="E119">
-        <v>1984</v>
-      </c>
-      <c r="G119" t="s">
-        <v>212</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B120">
-        <v>3</v>
-      </c>
-      <c r="C120" t="s">
-        <v>270</v>
-      </c>
-      <c r="D120" t="s">
-        <v>271</v>
-      </c>
-      <c r="E120">
-        <v>2016</v>
-      </c>
-      <c r="G120" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B121">
-        <v>3</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="E124">
+        <v>2003</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G124" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B125">
+        <v>5</v>
+      </c>
+      <c r="C125" t="s">
+        <v>233</v>
+      </c>
+      <c r="D125" t="s">
+        <v>261</v>
+      </c>
+      <c r="E125">
+        <v>1994</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G125" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B126">
+        <v>5</v>
+      </c>
+      <c r="C126" t="s">
+        <v>234</v>
+      </c>
+      <c r="D126" t="s">
+        <v>262</v>
+      </c>
+      <c r="E126">
+        <v>2018</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G126" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B127">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>236</v>
+      </c>
+      <c r="D127" t="s">
+        <v>263</v>
+      </c>
+      <c r="E127">
+        <v>1971</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G127" t="s">
+        <v>193</v>
+      </c>
+      <c r="H127" t="s">
+        <v>490</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B128">
+        <v>6</v>
+      </c>
+      <c r="C128" t="s">
+        <v>239</v>
+      </c>
+      <c r="D128" t="s">
+        <v>265</v>
+      </c>
+      <c r="E128">
+        <v>1920</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="G128" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B129">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>272</v>
+      </c>
+      <c r="D129" t="s">
         <v>273</v>
       </c>
-      <c r="D121" t="s">
-        <v>274</v>
-      </c>
-      <c r="E121">
-        <v>1984</v>
-      </c>
-      <c r="G121" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B122">
-        <v>3</v>
-      </c>
-      <c r="C122" t="s">
-        <v>277</v>
-      </c>
-      <c r="D122" t="s">
-        <v>279</v>
-      </c>
-      <c r="E122">
-        <v>1982</v>
-      </c>
-      <c r="G122" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B123">
-        <v>3</v>
-      </c>
-      <c r="C123" t="s">
-        <v>281</v>
-      </c>
-      <c r="D123" t="s">
-        <v>236</v>
-      </c>
-      <c r="E123">
-        <v>2011</v>
-      </c>
-      <c r="G123" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B124">
-        <v>3</v>
-      </c>
-      <c r="C124" t="s">
-        <v>285</v>
-      </c>
-      <c r="D124" t="s">
-        <v>341</v>
-      </c>
-      <c r="E124">
-        <v>1984</v>
-      </c>
-      <c r="G124" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B125">
-        <v>3</v>
-      </c>
-      <c r="C125" t="s">
-        <v>287</v>
-      </c>
-      <c r="D125" t="s">
-        <v>288</v>
-      </c>
-      <c r="E125">
-        <v>1985</v>
-      </c>
-      <c r="G125" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B126">
-        <v>3</v>
-      </c>
-      <c r="C126" t="s">
-        <v>289</v>
-      </c>
-      <c r="D126" t="s">
-        <v>290</v>
-      </c>
-      <c r="E126">
-        <v>2008</v>
-      </c>
-      <c r="G126" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B127">
-        <v>3</v>
-      </c>
-      <c r="C127" t="s">
-        <v>291</v>
-      </c>
-      <c r="D127" t="s">
-        <v>292</v>
-      </c>
-      <c r="E127">
-        <v>1984</v>
-      </c>
-      <c r="G127" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B128">
-        <v>3</v>
-      </c>
-      <c r="C128" t="s">
-        <v>295</v>
-      </c>
-      <c r="D128" t="s">
-        <v>342</v>
-      </c>
-      <c r="E128">
-        <v>1961</v>
-      </c>
-      <c r="G128" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B129">
-        <v>3</v>
-      </c>
-      <c r="C129" t="s">
-        <v>296</v>
-      </c>
-      <c r="D129" t="s">
-        <v>298</v>
-      </c>
       <c r="E129">
-        <v>1971</v>
+        <v>1953</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="G129" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B130">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C130" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D130" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="E130">
-        <v>1939</v>
+        <v>1988</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="G130" t="s">
-        <v>212</v>
-      </c>
-      <c r="I130" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C131" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D131" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="E131">
-        <v>1998</v>
+        <v>1988</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="G131" t="s">
-        <v>212</v>
-      </c>
-      <c r="I131" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B132">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C132" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D132" t="s">
         <v>276</v>
@@ -3864,564 +4800,588 @@
       <c r="E132">
         <v>1983</v>
       </c>
+      <c r="F132" s="2" t="s">
+        <v>445</v>
+      </c>
       <c r="G132" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B133">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C133" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D133" t="s">
+        <v>198</v>
+      </c>
+      <c r="E133">
+        <v>2013</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="G133" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B134">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>231</v>
+      </c>
+      <c r="D134" t="s">
+        <v>257</v>
+      </c>
+      <c r="E134">
+        <v>1988</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G134" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B135">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>248</v>
+      </c>
+      <c r="D135" t="s">
         <v>278</v>
       </c>
-      <c r="E133">
-        <v>1988</v>
-      </c>
-      <c r="G133" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B134">
-        <v>5</v>
-      </c>
-      <c r="C134" t="s">
-        <v>253</v>
-      </c>
-      <c r="D134" t="s">
+      <c r="E135">
+        <v>1985</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G135" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B136">
+        <v>7</v>
+      </c>
+      <c r="C136" t="s">
+        <v>279</v>
+      </c>
+      <c r="D136" t="s">
+        <v>291</v>
+      </c>
+      <c r="E136">
+        <v>1986</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G136" t="s">
+        <v>193</v>
+      </c>
+      <c r="H136" t="s">
+        <v>492</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B137">
+        <v>7</v>
+      </c>
+      <c r="C137" t="s">
         <v>280</v>
       </c>
-      <c r="E134">
-        <v>2003</v>
-      </c>
-      <c r="G134" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B135">
-        <v>5</v>
-      </c>
-      <c r="C135" t="s">
-        <v>254</v>
-      </c>
-      <c r="D135" t="s">
+      <c r="D137" t="s">
+        <v>292</v>
+      </c>
+      <c r="E137">
+        <v>1889</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="G137" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B138">
+        <v>7</v>
+      </c>
+      <c r="C138" t="s">
+        <v>281</v>
+      </c>
+      <c r="D138" t="s">
+        <v>293</v>
+      </c>
+      <c r="E138">
+        <v>1990</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G138" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B139">
+        <v>7</v>
+      </c>
+      <c r="C139" t="s">
         <v>282</v>
-      </c>
-      <c r="E135">
-        <v>1994</v>
-      </c>
-      <c r="G135" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B136">
-        <v>5</v>
-      </c>
-      <c r="C136" t="s">
-        <v>255</v>
-      </c>
-      <c r="D136" t="s">
-        <v>283</v>
-      </c>
-      <c r="E136">
-        <v>2018</v>
-      </c>
-      <c r="G136" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B137">
-        <v>6</v>
-      </c>
-      <c r="C137" t="s">
-        <v>257</v>
-      </c>
-      <c r="D137" t="s">
-        <v>284</v>
-      </c>
-      <c r="E137">
-        <v>1971</v>
-      </c>
-      <c r="G137" t="s">
-        <v>212</v>
-      </c>
-      <c r="I137" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B138">
-        <v>6</v>
-      </c>
-      <c r="C138" t="s">
-        <v>260</v>
-      </c>
-      <c r="D138" t="s">
-        <v>286</v>
-      </c>
-      <c r="E138">
-        <v>1920</v>
-      </c>
-      <c r="G138" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B139">
-        <v>6</v>
-      </c>
-      <c r="C139" t="s">
-        <v>293</v>
       </c>
       <c r="D139" t="s">
         <v>294</v>
       </c>
       <c r="E139">
-        <v>1953</v>
+        <v>2017</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="G139" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B140">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="D140" t="s">
-        <v>278</v>
+        <v>454</v>
       </c>
       <c r="E140">
-        <v>1988</v>
+        <v>1899</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>453</v>
       </c>
       <c r="G140" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B141">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>455</v>
       </c>
       <c r="D141" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="E141">
-        <v>1988</v>
+        <v>2009</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>456</v>
       </c>
       <c r="G141" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C142" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="D142" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="E142">
         <v>1983</v>
       </c>
+      <c r="F142" s="2" t="s">
+        <v>457</v>
+      </c>
       <c r="G142" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B143">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C143" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="D143" t="s">
-        <v>217</v>
+        <v>295</v>
       </c>
       <c r="E143">
-        <v>2013</v>
+        <v>1985</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>456</v>
       </c>
       <c r="G143" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B144">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C144" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="D144" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="E144">
-        <v>1988</v>
+        <v>1994</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="G144" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B145">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="D145" t="s">
+        <v>297</v>
+      </c>
+      <c r="E145">
+        <v>2010</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="G145" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="146" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B146">
+        <v>8</v>
+      </c>
+      <c r="C146" t="s">
+        <v>298</v>
+      </c>
+      <c r="D146" t="s">
+        <v>311</v>
+      </c>
+      <c r="E146">
+        <v>1987</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G146" t="s">
+        <v>193</v>
+      </c>
+      <c r="H146" t="s">
+        <v>491</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="147" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B147">
+        <v>8</v>
+      </c>
+      <c r="C147" t="s">
         <v>299</v>
       </c>
-      <c r="E145">
-        <v>1985</v>
-      </c>
-      <c r="G145" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B146">
-        <v>7</v>
-      </c>
-      <c r="C146" t="s">
+      <c r="D147" t="s">
+        <v>310</v>
+      </c>
+      <c r="E147">
+        <v>1967</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="G147" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="148" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B148">
+        <v>8</v>
+      </c>
+      <c r="C148" t="s">
         <v>300</v>
       </c>
-      <c r="D146" t="s">
-        <v>314</v>
-      </c>
-      <c r="E146">
-        <v>1986</v>
-      </c>
-      <c r="G146" t="s">
-        <v>212</v>
-      </c>
-      <c r="I146" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B147">
-        <v>7</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="D148" t="s">
+        <v>309</v>
+      </c>
+      <c r="E148">
+        <v>1974</v>
+      </c>
+      <c r="F148" t="s">
+        <v>462</v>
+      </c>
+      <c r="G148" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="149" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B149">
+        <v>8</v>
+      </c>
+      <c r="C149" t="s">
         <v>301</v>
       </c>
-      <c r="D147" t="s">
-        <v>315</v>
-      </c>
-      <c r="E147" t="s">
-        <v>337</v>
-      </c>
-      <c r="G147" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B148">
-        <v>7</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="D149" t="s">
+        <v>308</v>
+      </c>
+      <c r="E149">
+        <v>2019</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G149" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="150" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B150">
+        <v>8</v>
+      </c>
+      <c r="C150" t="s">
         <v>302</v>
       </c>
-      <c r="D148" t="s">
-        <v>316</v>
-      </c>
-      <c r="E148">
-        <v>1997</v>
-      </c>
-      <c r="G148" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B149">
-        <v>7</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="D150" t="s">
+        <v>307</v>
+      </c>
+      <c r="E150">
+        <v>2011</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G150" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="151" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B151">
+        <v>8</v>
+      </c>
+      <c r="C151" t="s">
         <v>303</v>
       </c>
-      <c r="D149" t="s">
-        <v>317</v>
-      </c>
-      <c r="E149">
-        <v>2017</v>
-      </c>
-      <c r="G149" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B150">
-        <v>7</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="D151" t="s">
+        <v>306</v>
+      </c>
+      <c r="E151">
+        <v>1978</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="G151" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="152" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B152">
+        <v>8</v>
+      </c>
+      <c r="C152" t="s">
         <v>304</v>
       </c>
-      <c r="D150" t="s">
-        <v>248</v>
-      </c>
-      <c r="E150" t="s">
-        <v>338</v>
-      </c>
-      <c r="G150" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B151">
-        <v>7</v>
-      </c>
-      <c r="C151" t="s">
-        <v>309</v>
-      </c>
-      <c r="D151" t="s">
-        <v>318</v>
-      </c>
-      <c r="E151">
-        <v>2009</v>
-      </c>
-      <c r="G151" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B152">
-        <v>7</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
         <v>305</v>
       </c>
-      <c r="D152" t="s">
-        <v>339</v>
-      </c>
       <c r="E152">
-        <v>1983</v>
+        <v>2019</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>466</v>
       </c>
       <c r="G152" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B153">
-        <v>7</v>
-      </c>
-      <c r="C153" t="s">
-        <v>311</v>
-      </c>
-      <c r="D153" t="s">
-        <v>318</v>
-      </c>
-      <c r="E153">
-        <v>1985</v>
-      </c>
-      <c r="G153" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B154">
-        <v>7</v>
-      </c>
-      <c r="C154" t="s">
-        <v>310</v>
-      </c>
-      <c r="D154" t="s">
-        <v>319</v>
-      </c>
-      <c r="E154">
-        <v>1994</v>
-      </c>
-      <c r="G154" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B155">
-        <v>7</v>
-      </c>
-      <c r="C155" t="s">
-        <v>312</v>
-      </c>
-      <c r="D155" t="s">
-        <v>320</v>
-      </c>
-      <c r="E155" t="s">
-        <v>340</v>
-      </c>
-      <c r="G155" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B156">
-        <v>7</v>
-      </c>
-      <c r="C156" t="s">
-        <v>313</v>
-      </c>
-      <c r="D156" t="s">
-        <v>321</v>
-      </c>
-      <c r="E156">
-        <v>2010</v>
-      </c>
-      <c r="G156" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B157">
-        <v>8</v>
-      </c>
-      <c r="C157" t="s">
-        <v>322</v>
-      </c>
-      <c r="D157" t="s">
-        <v>336</v>
-      </c>
-      <c r="E157">
-        <v>1987</v>
-      </c>
-      <c r="G157" t="s">
-        <v>212</v>
-      </c>
-      <c r="I157" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B158">
-        <v>8</v>
-      </c>
-      <c r="C158" t="s">
-        <v>323</v>
-      </c>
-      <c r="D158" t="s">
-        <v>335</v>
-      </c>
-      <c r="E158">
-        <v>1967</v>
-      </c>
-      <c r="G158" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B159">
-        <v>8</v>
-      </c>
-      <c r="C159" t="s">
-        <v>324</v>
-      </c>
-      <c r="D159" t="s">
-        <v>334</v>
-      </c>
-      <c r="E159">
-        <v>1974</v>
-      </c>
-      <c r="G159" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B160">
-        <v>8</v>
-      </c>
-      <c r="C160" t="s">
-        <v>325</v>
-      </c>
-      <c r="D160" t="s">
-        <v>333</v>
-      </c>
-      <c r="E160">
-        <v>2019</v>
-      </c>
-      <c r="G160" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B161">
-        <v>8</v>
-      </c>
-      <c r="C161" t="s">
-        <v>326</v>
-      </c>
-      <c r="D161" t="s">
-        <v>332</v>
-      </c>
-      <c r="E161">
-        <v>2011</v>
-      </c>
-      <c r="G161" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="162" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B162">
-        <v>8</v>
-      </c>
-      <c r="C162" t="s">
-        <v>327</v>
-      </c>
-      <c r="D162" t="s">
-        <v>331</v>
-      </c>
-      <c r="E162">
-        <v>1978</v>
-      </c>
-      <c r="G162" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="163" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B163">
-        <v>8</v>
-      </c>
-      <c r="C163" t="s">
-        <v>328</v>
-      </c>
-      <c r="D163" t="s">
-        <v>330</v>
-      </c>
-      <c r="E163">
-        <v>2019</v>
-      </c>
-      <c r="G163" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B164">
-        <v>8</v>
-      </c>
-      <c r="C164" t="s">
-        <v>329</v>
-      </c>
-      <c r="D164" t="s">
-        <v>160</v>
-      </c>
-      <c r="E164">
-        <v>2010</v>
-      </c>
-      <c r="G164" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F37" r:id="rId1" display="https://www.google.com/imgres?q=whip%20it%20song%20devo&amp;imgurl=https%3A%2F%2Fi.scdn.co%2Fimage%2Fab67616d0000b273f4f1f36551dd41c5442c2a2f&amp;imgrefurl=https%3A%2F%2Fopen.spotify.com%2Fintl-es%2Ftrack%2F4sscDOZCkbLSlDqcCgUJnX&amp;docid=oVDtJaAIUHe9CM&amp;tbnid=NE6pXn75oAFC6M&amp;vet=12ahUKEwjnuuLHm7eVAxU9-AIHHaDgB_wQnPAOegQINBAA..i&amp;w=640&amp;h=640&amp;hcb=2&amp;ved=2ahUKEwjnuuLHm7eVAxU9-AIHHaDgB_wQnPAOegQINBAA" xr:uid="{CEABFEC0-7895-4F62-BED5-C9D13E7A5041}"/>
+    <hyperlink ref="F38" r:id="rId2" display="https://www.google.com/imgres?q=Just%20Another%20Day%09Oingo%20Boingo%0D%0Asong&amp;imgurl=https%3A%2F%2Fi.scdn.co%2Fimage%2Fab67616d0000b273117c53d4921791280aad03ba&amp;imgrefurl=https%3A%2F%2Fopen.spotify.com%2Ftrack%2F6w6I3AFRv7tQMmUTgAghUB&amp;docid=vJLhF4tnMRvm-M&amp;tbnid=40E8TCeBLB_VkM&amp;vet=12ahUKEwixtbnWm7eVAxVK-QIHHfh-CH0QnPAOegQINBAA..i&amp;w=630&amp;h=640&amp;hcb=2&amp;ved=2ahUKEwixtbnWm7eVAxVK-QIHHfh-CH0QnPAOegQINBAA" xr:uid="{8BB839B5-2F19-428C-B6BA-02B3906E6EC7}"/>
+    <hyperlink ref="F39" r:id="rId3" display="https://www.google.com/imgres?q=Talking%20In%20Your%20Sleep%09The%20Romantics%0D%0A&amp;imgurl=https%3A%2F%2Fupload.wikimedia.org%2Fwikipedia%2Fen%2F0%2F0a%2FThe_romantics-talking_in_your_sleep_s.jpg&amp;imgrefurl=https%3A%2F%2Fen.wikipedia.org%2Fwiki%2FTalking_in_Your_Sleep_(The_Romantics_song)&amp;docid=9pp60CM4E4S99M&amp;tbnid=TVKJOnLmoOQXaM&amp;vet=12ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA..i&amp;w=315&amp;h=317&amp;hcb=2&amp;ved=2ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA" xr:uid="{548F9394-8FD7-4E5E-A739-AA20C7B462E3}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{EBEE5C6C-7AE1-46AA-8945-75B2FB1A63D8}"/>
+    <hyperlink ref="F4" r:id="rId5" xr:uid="{8E99786A-9072-4750-9A6C-6559D69DA39A}"/>
+    <hyperlink ref="F5" r:id="rId6" xr:uid="{E389C741-7024-4418-9F09-2C76960AC9E8}"/>
+    <hyperlink ref="F6" r:id="rId7" xr:uid="{D6111C2C-4FEE-4C47-8800-77251E75106D}"/>
+    <hyperlink ref="F7" r:id="rId8" xr:uid="{AEA3E744-2CEB-457D-AD24-B6A533A5C808}"/>
+    <hyperlink ref="F8" r:id="rId9" xr:uid="{9C9B4333-5A87-4680-A85B-816215193AFD}"/>
+    <hyperlink ref="F9" r:id="rId10" xr:uid="{A1CBDBEE-ED89-41AF-885C-E3A5AB9EEE6C}"/>
+    <hyperlink ref="F10" r:id="rId11" xr:uid="{EC1100A9-DC17-47F7-89D1-273634B2F1E4}"/>
+    <hyperlink ref="F11" r:id="rId12" xr:uid="{80392B61-6154-4372-B0B1-BC3B12DD42C9}"/>
+    <hyperlink ref="F12" r:id="rId13" xr:uid="{1EA8F47E-42E2-4B89-9C55-95996E94BC69}"/>
+    <hyperlink ref="F13" r:id="rId14" xr:uid="{776710CF-C4B3-4EB6-B12D-371FA51D9C8A}"/>
+    <hyperlink ref="F14" r:id="rId15" xr:uid="{A389CAB8-73B1-41A2-8B9E-D03C2FA0692A}"/>
+    <hyperlink ref="F15" r:id="rId16" xr:uid="{8835943D-AC76-4CE9-86D8-3EC3BE7CC9ED}"/>
+    <hyperlink ref="F16" r:id="rId17" xr:uid="{C94019BC-9807-43B6-A974-A3D3B5F45759}"/>
+    <hyperlink ref="F17" r:id="rId18" xr:uid="{DCCF46BD-AA23-4C33-8075-2398EFBDE54D}"/>
+    <hyperlink ref="F18" r:id="rId19" xr:uid="{092BE224-6EBA-4689-B715-35D2D7200833}"/>
+    <hyperlink ref="F19" r:id="rId20" xr:uid="{1E2B7EDB-5485-4DFA-9FFB-5214B043808B}"/>
+    <hyperlink ref="F20" r:id="rId21" xr:uid="{9CC7FD77-85C5-4532-AC7E-6D64B94A73DA}"/>
+    <hyperlink ref="F21" r:id="rId22" xr:uid="{503607D2-D0F3-4953-A5E0-7F0344CDCAE9}"/>
+    <hyperlink ref="F22" r:id="rId23" xr:uid="{8E5F0418-536B-4FF3-A996-CE1EB8294567}"/>
+    <hyperlink ref="F23" r:id="rId24" xr:uid="{67E7B28B-76EC-4DAB-A28C-52C22340CB79}"/>
+    <hyperlink ref="F24" r:id="rId25" xr:uid="{103330D5-65DD-410E-9423-5170A00048F1}"/>
+    <hyperlink ref="F25" r:id="rId26" xr:uid="{411DB0EC-E527-437B-AF72-3B4D05BC289A}"/>
+    <hyperlink ref="F26" r:id="rId27" xr:uid="{9B276B0E-ABB5-43D0-A22A-5D2057F83E31}"/>
+    <hyperlink ref="F27" r:id="rId28" xr:uid="{E19A0CD3-0EDC-4A4F-A844-F1D03D8823A4}"/>
+    <hyperlink ref="F28" r:id="rId29" xr:uid="{AA103AEB-1054-4A64-8EF7-974C6E4789CD}"/>
+    <hyperlink ref="F29" r:id="rId30" xr:uid="{BF027D9D-2BFB-44CC-9FC5-4DB20C7997BA}"/>
+    <hyperlink ref="F30" r:id="rId31" xr:uid="{5C8E4A2F-AE62-4DB9-970B-8E120C3B4CBA}"/>
+    <hyperlink ref="F31" r:id="rId32" xr:uid="{8711ACB2-7F8B-4071-8FA8-15679174B987}"/>
+    <hyperlink ref="F32" r:id="rId33" xr:uid="{D1E17956-8344-452C-B808-6BFC6BF0285C}"/>
+    <hyperlink ref="F33" r:id="rId34" xr:uid="{54E01A57-0C9C-47DA-9648-1D79AAAD7B70}"/>
+    <hyperlink ref="F34" r:id="rId35" xr:uid="{7D0875F2-4D85-4B8E-BEAA-CA3284A33D88}"/>
+    <hyperlink ref="F35" r:id="rId36" xr:uid="{70DAD2EE-FA95-4BC6-93B7-4C84DD8747B7}"/>
+    <hyperlink ref="F36" r:id="rId37" xr:uid="{AC32B9EF-88B8-4C0A-98BC-CFC4342416E9}"/>
+    <hyperlink ref="F40" r:id="rId38" xr:uid="{9B7E7A00-F04F-4632-9441-02133DD2069A}"/>
+    <hyperlink ref="F41" r:id="rId39" xr:uid="{9E105A04-B7A9-4D80-8AA4-3D8CFFF2C496}"/>
+    <hyperlink ref="F42" r:id="rId40" xr:uid="{7A1E96B4-A984-4381-A54D-C88B6172382D}"/>
+    <hyperlink ref="F43" r:id="rId41" xr:uid="{CBC05CE3-4B62-44F0-B063-2574BCB33593}"/>
+    <hyperlink ref="F44" r:id="rId42" xr:uid="{C8BE8B1E-E573-40AF-8628-9BAA53CE7BF9}"/>
+    <hyperlink ref="F45" r:id="rId43" xr:uid="{9A396326-06E9-40BE-8577-73DF57B60957}"/>
+    <hyperlink ref="F46" r:id="rId44" xr:uid="{5F30CD71-8849-4815-B084-861DDB31A00E}"/>
+    <hyperlink ref="F47" r:id="rId45" xr:uid="{164211E1-D250-4210-B3B4-21CD055EB93D}"/>
+    <hyperlink ref="F48" r:id="rId46" xr:uid="{37416CE2-DCC6-4A0B-B613-0BFD7CA121A0}"/>
+    <hyperlink ref="F49" r:id="rId47" xr:uid="{65706E76-0698-4A71-8390-F4996B8235F1}"/>
+    <hyperlink ref="F50" r:id="rId48" xr:uid="{F960FAED-6B14-454F-AC20-81FEB88BDF87}"/>
+    <hyperlink ref="F51" r:id="rId49" xr:uid="{4B736073-86A5-4921-BE5B-E6D8A077EA0D}"/>
+    <hyperlink ref="F52" r:id="rId50" xr:uid="{486E5C1E-77FF-443E-B757-3105017F1489}"/>
+    <hyperlink ref="F53" r:id="rId51" xr:uid="{A9E9277D-36BE-42E2-BE44-063D425DE1BF}"/>
+    <hyperlink ref="F54" r:id="rId52" xr:uid="{8C6D7D85-F8B3-4CC9-93DA-17BDCBC58E65}"/>
+    <hyperlink ref="F55" r:id="rId53" xr:uid="{09C00082-4016-4764-BD7F-129F474D6D98}"/>
+    <hyperlink ref="F56" r:id="rId54" xr:uid="{01F04D16-6013-436A-9340-AE07AB3FBDF2}"/>
+    <hyperlink ref="F57" r:id="rId55" xr:uid="{C0015A97-1B83-4AB5-9A76-52566F5EB733}"/>
+    <hyperlink ref="F58" r:id="rId56" xr:uid="{DF9A635C-126B-4B81-BD14-4E5BDE57D360}"/>
+    <hyperlink ref="F59" r:id="rId57" xr:uid="{70FDC6F1-E3D1-46EC-A3F7-57E7E4DD02BE}"/>
+    <hyperlink ref="F60" r:id="rId58" xr:uid="{AF2CB4DB-0F63-4EFA-908F-049475EFA9E7}"/>
+    <hyperlink ref="F61" r:id="rId59" xr:uid="{A2C1036A-F31C-4B28-AA15-FC5BC296D308}"/>
+    <hyperlink ref="F62" r:id="rId60" xr:uid="{F1C2A288-6AB7-4D6C-9DF4-2F81136001BD}"/>
+    <hyperlink ref="F63" r:id="rId61" xr:uid="{980F9DDA-5D33-469E-B032-9E24D7C1B2E0}"/>
+    <hyperlink ref="F64" r:id="rId62" xr:uid="{538A9B5F-8314-4735-9930-B2ED398D3CD6}"/>
+    <hyperlink ref="F65" r:id="rId63" xr:uid="{4E12FE13-4C11-4998-9366-8202DF690B80}"/>
+    <hyperlink ref="F66" r:id="rId64" xr:uid="{B7B17A4A-68ED-4D4B-A5D1-BB12074BA9DC}"/>
+    <hyperlink ref="F67" r:id="rId65" xr:uid="{4BFD0EEB-7470-46EC-AC56-0BFBAD347B3B}"/>
+    <hyperlink ref="F68" r:id="rId66" xr:uid="{5C3BD910-6A90-41E1-9965-D7888B48A918}"/>
+    <hyperlink ref="F69" r:id="rId67" xr:uid="{D1E4D1EA-DECE-4B20-9801-C74F2F7664F2}"/>
+    <hyperlink ref="F70" r:id="rId68" xr:uid="{C79B78AE-8F3C-44C1-9E11-45E5112D89A4}"/>
+    <hyperlink ref="F71" r:id="rId69" xr:uid="{3E12B6B4-DA38-4480-A22C-370C8F2F8F0B}"/>
+    <hyperlink ref="F72" r:id="rId70" xr:uid="{73687896-4DBD-4801-AB53-94749802083B}"/>
+    <hyperlink ref="F73" r:id="rId71" xr:uid="{CDA99111-643A-447C-A27B-1B44951203B8}"/>
+    <hyperlink ref="F74" r:id="rId72" xr:uid="{12A88964-AA18-4EBE-9452-CF60B585E9CA}"/>
+    <hyperlink ref="F75" r:id="rId73" xr:uid="{B19667DD-32E8-40E0-A3F6-C22283F24AFC}"/>
+    <hyperlink ref="F76" r:id="rId74" xr:uid="{1FA82F97-C56B-4B4E-B3E5-CBDAC47A84BC}"/>
+    <hyperlink ref="F77" r:id="rId75" xr:uid="{A2587DCF-2761-4AE4-97B9-A4180226846F}"/>
+    <hyperlink ref="F78" r:id="rId76" xr:uid="{D3AE1623-0079-44C6-82CE-7A066EBE1E1D}"/>
+    <hyperlink ref="F79" r:id="rId77" xr:uid="{B0C88619-9451-42AA-A31E-586750F39727}"/>
+    <hyperlink ref="F80" r:id="rId78" xr:uid="{96F42F96-7BCF-405E-A95E-E229F3807090}"/>
+    <hyperlink ref="F81" r:id="rId79" xr:uid="{07A399C2-C32C-4E8E-AE29-85A548019F11}"/>
+    <hyperlink ref="F82" r:id="rId80" xr:uid="{672178A5-0536-4449-91A0-AADCB5150688}"/>
+    <hyperlink ref="F83" r:id="rId81" xr:uid="{E17F8816-1F9E-4CF4-B6C8-B8BE6B73C861}"/>
+    <hyperlink ref="F84" r:id="rId82" xr:uid="{4D074580-7E0A-4CB4-AF7A-5D22387A2DEF}"/>
+    <hyperlink ref="F85" r:id="rId83" xr:uid="{F50D187A-28F9-4FB3-96C5-9F1A0D4B3C0A}"/>
+    <hyperlink ref="F86" r:id="rId84" xr:uid="{BD92A685-7644-4EAE-A71C-6282DDF46E36}"/>
+    <hyperlink ref="F87" r:id="rId85" xr:uid="{BCA2468D-1173-4107-BFC1-D6222898C756}"/>
+    <hyperlink ref="F88" r:id="rId86" xr:uid="{B0B7B318-EDA2-418D-AF9E-E708AA943AD8}"/>
+    <hyperlink ref="F89" r:id="rId87" xr:uid="{CA190611-3FEA-4B3C-BDEA-E894BA7E0B51}"/>
+    <hyperlink ref="F90" r:id="rId88" xr:uid="{EE0AD7DB-964D-46E8-AC21-3C625DFB4892}"/>
+    <hyperlink ref="F91" r:id="rId89" xr:uid="{4F86780C-AC81-4798-89B7-7BBEF3BA5125}"/>
+    <hyperlink ref="F92" r:id="rId90" xr:uid="{5AA9B59F-2554-41E8-8E84-275A682D8356}"/>
+    <hyperlink ref="F93" r:id="rId91" xr:uid="{5399AE5C-7E51-40E3-8730-0E0DFE0EDAA3}"/>
+    <hyperlink ref="F94" r:id="rId92" xr:uid="{213CB07D-6520-4678-A8C3-F3FE331A2FE4}"/>
+    <hyperlink ref="F95" r:id="rId93" xr:uid="{BE5DBFD0-A4E1-4B6D-B997-195C31C9033F}"/>
+    <hyperlink ref="F96" r:id="rId94" xr:uid="{2D2FD5DC-AA4B-437C-864C-914726CE0B19}"/>
+    <hyperlink ref="F97" r:id="rId95" xr:uid="{9B7DBB46-388A-4A6E-876B-245B033C593C}"/>
+    <hyperlink ref="F98" r:id="rId96" xr:uid="{E64AE5F5-ED9E-4F89-80D3-36B2ADCA765A}"/>
+    <hyperlink ref="F99" r:id="rId97" xr:uid="{FAADB430-0C4D-462C-A5E0-327E69331ECD}"/>
+    <hyperlink ref="F100" r:id="rId98" xr:uid="{E4F11F6B-F74C-41BB-BA4A-726EF9BFF135}"/>
+    <hyperlink ref="F101" r:id="rId99" xr:uid="{963E28A5-4A36-4DA7-A39E-4EB6A4972B5B}"/>
+    <hyperlink ref="F102" r:id="rId100" xr:uid="{E53FAA3F-14A0-4FFC-9041-A63681EA3AAD}"/>
+    <hyperlink ref="F103" r:id="rId101" xr:uid="{BE7F5E36-A70D-4969-BD9A-4969EE31ECD2}"/>
+    <hyperlink ref="F104" r:id="rId102" xr:uid="{D094EF61-2138-46F1-8129-219CF6574411}"/>
+    <hyperlink ref="F105" r:id="rId103" xr:uid="{2BDE5563-26C2-4BCD-8728-D13E536DFDE8}"/>
+    <hyperlink ref="F106" r:id="rId104" xr:uid="{BE46DC8F-C1C3-4C30-9CCD-596FD61880DF}"/>
+    <hyperlink ref="F107" r:id="rId105" xr:uid="{B04DEA0D-650E-45A8-97A8-8A239FB454E8}"/>
+    <hyperlink ref="F108" r:id="rId106" xr:uid="{C7AB48FA-187E-4EC7-BBC0-C34C48E804B6}"/>
+    <hyperlink ref="F109" r:id="rId107" xr:uid="{12B5E0F7-71D4-44F2-ABBC-5CD1B1E15630}"/>
+    <hyperlink ref="F110" r:id="rId108" xr:uid="{AF7460AD-2169-4389-9102-CC9996D382C0}"/>
+    <hyperlink ref="F111" r:id="rId109" xr:uid="{D65C6847-A23D-458D-8720-D0FEE3F10F86}"/>
+    <hyperlink ref="F112" r:id="rId110" xr:uid="{C1F6F441-ECE2-46B7-BC01-27B962C4AB16}"/>
+    <hyperlink ref="F113" r:id="rId111" xr:uid="{C966B0A2-541E-4E32-AF5F-DBC955C1DB06}"/>
+    <hyperlink ref="F114" r:id="rId112" xr:uid="{5E6F5E0F-3CD7-483E-A6EF-F2101F8078B3}"/>
+    <hyperlink ref="F115" r:id="rId113" xr:uid="{08215017-D939-4531-87ED-9E8425D34601}"/>
+    <hyperlink ref="F116" r:id="rId114" xr:uid="{C2445B34-A362-448C-89D0-B78ABDA67E46}"/>
+    <hyperlink ref="F117" r:id="rId115" xr:uid="{2F22D7CD-C26B-4E97-87B2-D69CCE84F53B}"/>
+    <hyperlink ref="F118" r:id="rId116" xr:uid="{C0E1AECB-DF64-4EEB-BDD8-1F0BAD6C81B5}"/>
+    <hyperlink ref="F119" r:id="rId117" xr:uid="{03DD02FA-B4B9-46AB-91A0-E76930C094A8}"/>
+    <hyperlink ref="F120" r:id="rId118" xr:uid="{3ECDC44E-949F-42C0-B986-4C558423CBBE}"/>
+    <hyperlink ref="F121" r:id="rId119" xr:uid="{A0851054-AF48-43AF-BA33-D081F9C766B9}"/>
+    <hyperlink ref="F122" r:id="rId120" xr:uid="{BEBB832A-C39C-4F79-B145-9B36E12C3CB1}"/>
+    <hyperlink ref="F123" r:id="rId121" xr:uid="{E4FDC80C-8C6D-4C03-B8DB-938614A67889}"/>
+    <hyperlink ref="F124" r:id="rId122" xr:uid="{E25353C4-311A-4A6C-9B26-00C1E48C823B}"/>
+    <hyperlink ref="F125" r:id="rId123" xr:uid="{051E01FE-D93B-491B-AC40-D7D8ED72239E}"/>
+    <hyperlink ref="F126" r:id="rId124" xr:uid="{3603EB80-64EC-4629-A1B4-7AE6ADCC7114}"/>
+    <hyperlink ref="F127" r:id="rId125" xr:uid="{03E3762D-87C1-41B4-921F-7361AFAFBF2F}"/>
+    <hyperlink ref="F128" r:id="rId126" xr:uid="{A4B68288-E639-49F4-993C-29EAA4072A71}"/>
+    <hyperlink ref="F129" r:id="rId127" xr:uid="{C9D31F1C-A8CB-4799-A2A4-68E0945ABAAE}"/>
+    <hyperlink ref="F130" r:id="rId128" xr:uid="{FD353834-3E91-4CBB-A6C4-8B495E23D124}"/>
+    <hyperlink ref="F131" r:id="rId129" xr:uid="{7B0E69D1-6FDF-4BBA-9AA4-C5A6BF27C928}"/>
+    <hyperlink ref="F132" r:id="rId130" xr:uid="{9EBB9C49-BCBE-4EB8-BDB2-643167D609F8}"/>
+    <hyperlink ref="F133" r:id="rId131" xr:uid="{4DD7AB03-5DF6-4762-92E4-60B9EC6085F5}"/>
+    <hyperlink ref="F134" r:id="rId132" xr:uid="{ED8F2DB2-2B42-4883-9309-09AED4183D23}"/>
+    <hyperlink ref="F135" r:id="rId133" xr:uid="{A9AE5049-EC61-41A6-8788-F4B50355FA8D}"/>
+    <hyperlink ref="F136" r:id="rId134" xr:uid="{667027A3-4CF9-4B8A-A3FE-993C565D0F4C}"/>
+    <hyperlink ref="F137" r:id="rId135" xr:uid="{F25C4A50-CBE2-4E7A-859B-2FD1E573F254}"/>
+    <hyperlink ref="F138" r:id="rId136" xr:uid="{75FE179B-AF3B-4843-95BD-3EED8C14F364}"/>
+    <hyperlink ref="F139" r:id="rId137" xr:uid="{BE8AAB48-8749-40A3-AC68-AF790396A474}"/>
+    <hyperlink ref="F140" r:id="rId138" xr:uid="{71DD0714-9997-4016-9594-D53081FBA758}"/>
+    <hyperlink ref="F141" r:id="rId139" xr:uid="{7D4236B4-C6D2-4D9E-87D3-21CE2879F2B7}"/>
+    <hyperlink ref="F142" r:id="rId140" xr:uid="{AB78A0F2-0618-4D77-A42C-F41159E73520}"/>
+    <hyperlink ref="F143" r:id="rId141" xr:uid="{951D3B33-2808-4219-B8C0-6A78623E5AA1}"/>
+    <hyperlink ref="F144" r:id="rId142" xr:uid="{A9CE9CF3-160D-4B9F-B8BE-5E531859664C}"/>
+    <hyperlink ref="F145" r:id="rId143" xr:uid="{7A3502EB-AF45-4EE3-88E8-17228934C08E}"/>
+    <hyperlink ref="F146" r:id="rId144" xr:uid="{F89DC979-7339-4628-903D-928FCCCADEE5}"/>
+    <hyperlink ref="F147" r:id="rId145" xr:uid="{D2CACEA3-B167-4FE3-A994-3AD59A20A9A7}"/>
+    <hyperlink ref="F149" r:id="rId146" xr:uid="{22AC07A4-5F12-41FA-8FA8-D4F00424A9EC}"/>
+    <hyperlink ref="F150" r:id="rId147" xr:uid="{357908BA-3A52-4D80-B702-8F516D20FE4D}"/>
+    <hyperlink ref="F151" r:id="rId148" xr:uid="{30560881-6166-4C8F-84C3-DB257B037A99}"/>
+    <hyperlink ref="F152" r:id="rId149" xr:uid="{40EBB7C0-3D94-4005-BF13-1726CA98A382}"/>
+    <hyperlink ref="J146" r:id="rId150" xr:uid="{A0AAB73C-0E04-4F9C-A00E-1ECD18CD39DB}"/>
+    <hyperlink ref="J136" r:id="rId151" xr:uid="{208E28B7-2A86-42C6-8126-3F2AE9DA2E16}"/>
+    <hyperlink ref="J127" r:id="rId152" xr:uid="{3F6E69B2-FCE2-4047-A391-15513C571279}"/>
+    <hyperlink ref="J121" r:id="rId153" xr:uid="{E650C24A-5A75-4844-AD6D-D5FCDBCA2FD3}"/>
+    <hyperlink ref="J120" r:id="rId154" xr:uid="{53678A32-886B-4B53-B546-0001E24DF42B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4433,7 +5393,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/BASE DE DATOS - COMPUTACIONAL.xlsx
+++ b/BASE DE DATOS - COMPUTACIONAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85ad1e88542dc0fc/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1253" documentId="8_{865165E8-6C42-4D48-93DB-5FEF425A3BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FEFA1BB-8A9A-421E-8F0A-08CACCADCCE9}"/>
+  <xr:revisionPtr revIDLastSave="1281" documentId="8_{865165E8-6C42-4D48-93DB-5FEF425A3BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{209B90A9-D85A-4921-944F-69D90DF66370}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F7F6ACAE-8EDB-49D4-90A9-56CF5817301F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="519">
   <si>
     <t>Canción</t>
   </si>
@@ -1028,15 +1028,6 @@
     <t>Al Hazan</t>
   </si>
   <si>
-    <t>https://www.google.com/imgres?q=whip%20it%20song%20devo&amp;imgurl=https%3A%2F%2Fi.scdn.co%2Fimage%2Fab67616d0000b273f4f1f36551dd41c5442c2a2f&amp;imgrefurl=https%3A%2F%2Fopen.spotify.com%2Fintl-es%2Ftrack%2F4sscDOZCkbLSlDqcCgUJnX&amp;docid=oVDtJaAIUHe9CM&amp;tbnid=NE6pXn75oAFC6M&amp;vet=12ahUKEwjnuuLHm7eVAxU9-AIHHaDgB_wQnPAOegQINBAA..i&amp;w=640&amp;h=640&amp;hcb=2&amp;ved=2ahUKEwjnuuLHm7eVAxU9-AIHHaDgB_wQnPAOegQINBAA</t>
-  </si>
-  <si>
-    <t>https://www.google.com/imgres?q=Just%20Another%20Day%09Oingo%20Boingo%0D%0Asong&amp;imgurl=https%3A%2F%2Fi.scdn.co%2Fimage%2Fab67616d0000b273117c53d4921791280aad03ba&amp;imgrefurl=https%3A%2F%2Fopen.spotify.com%2Ftrack%2F6w6I3AFRv7tQMmUTgAghUB&amp;docid=vJLhF4tnMRvm-M&amp;tbnid=40E8TCeBLB_VkM&amp;vet=12ahUKEwixtbnWm7eVAxVK-QIHHfh-CH0QnPAOegQINBAA..i&amp;w=630&amp;h=640&amp;hcb=2&amp;ved=2ahUKEwixtbnWm7eVAxVK-QIHHfh-CH0QnPAOegQINBAA</t>
-  </si>
-  <si>
-    <t>https://www.google.com/imgres?q=Talking%20In%20Your%20Sleep%09The%20Romantics%0D%0A&amp;imgurl=https%3A%2F%2Fupload.wikimedia.org%2Fwikipedia%2Fen%2F0%2F0a%2FThe_romantics-talking_in_your_sleep_s.jpg&amp;imgrefurl=https%3A%2F%2Fen.wikipedia.org%2Fwiki%2FTalking_in_Your_Sleep_(The_Romantics_song)&amp;docid=9pp60CM4E4S99M&amp;tbnid=TVKJOnLmoOQXaM&amp;vet=12ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA..i&amp;w=315&amp;h=317&amp;hcb=2&amp;ved=2ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA</t>
-  </si>
-  <si>
     <t>https://i.scdn.co/image/ab67616d0000b273ac8529be93467378a0272698</t>
   </si>
   <si>
@@ -1578,6 +1569,75 @@
   </si>
   <si>
     <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQWkfd3nSk4Vi5jvoj8d_kdWec8v8Tl-A3XP-NmYVf-Vg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRrBdr4z8kytbkuuC3HtjKqqp_YI5TiFsL9ePLaGbDG3g&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ1wmor9nAg1Nwls5X5LC_b-LN63CMPQdfhFjfLtpr1Bg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS8WRY_3overiZHGr9VE5WTq280AzKMGTUQb05KhX_IUg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSm3vaExB-JG5TaAUzBe02u6iOQS_REbYbMfdXcxWwuPw&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyFq02ci1_S3jf6nvQ2sFlTA2SlJq1C551DYn9lYEa8w&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR_2ssc8M0Q9WTwK3Xr7P8ess6861dMkGe421iUE0NzxQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTC6YNDKxpIwAAy1KBBpYTjsIXTM09AXn6wFTJrQBK-Cg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSmJ1pTuafwvFaI5WPnNjZ-ppJeEaItwON7kvRxynXxww&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ4x2kOSO-kJra47x_i6wQ3s63fWV2bTzMSBU76X3HxMg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSztBTrcyfts4nCH8MivW_ukLOSbTylxDG5MfxxtprDjQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRMaP4mztKY-DMme7kliLwRyzJxtMxpG8oRIjURfeFemA&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT5dkQLs3BF5bANWdM-2hMAxZo8bj55hP1xf9vix915rQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTCVKuh7jhsvd81hQjvF5nTlaYRbP53f6o5m0vDw6xKOw&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTsJlMYZsJqMOHaeEPtQ5kgFurESyvxhw9rDaOj5dSwgQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ6CKHBPnRonW-HfLjJyAynzoF8XwE0cysWG0K-ierAFw&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQhu9QWMXmceKnAUD6ufU6T9nxpPR9YVlL1UsThGAtdCg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQZ10FjxfhRctRpYe45CjPD4Yyb8cv67L-tGS903OjpFg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSjyeZ3eFNTW-IM35Rrpy0fNOxjnWeHn8nKvLh5-LHtOg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR5qfN8cZ2KTjXs-djcLLdlDqOSGI7nD084X21diVyOGw&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ7d-0BwJKkWsI13lD8VHIijEpVbwYu9Q8_5CkltY5O4g&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://i.scdn.co/image/ab67616d0000b273f4f1f36551dd41c5442c2a2f</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/_5ap19n6QyyZjfsiJkQtErKgfkSUoejAtVH61gIhn90/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM3NzI3/MDMtMTM0MzgzMjU3/Ni0zNzc4LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/-3WfR8CIjGv16ClekcKf4WDL-wfbKLhuP_2DrlKzoRM/rs:fit/g:sm/q:90/h:600/w:600/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTYwNzUy/ODctMTQ0ODQ0Nzgy/Ny02ODUyLmpwZWc.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2050,13 +2110,13 @@
         <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I2" t="s">
         <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
@@ -2073,16 +2133,19 @@
         <v>1966</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G3" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
@@ -2099,7 +2162,7 @@
         <v>1967</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G4" t="s">
         <v>7</v>
@@ -2119,7 +2182,7 @@
         <v>1967</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G5" t="s">
         <v>7</v>
@@ -2139,7 +2202,7 @@
         <v>1970</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
@@ -2159,7 +2222,7 @@
         <v>1967</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G7" t="s">
         <v>7</v>
@@ -2179,7 +2242,7 @@
         <v>1982</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
@@ -2199,16 +2262,19 @@
         <v>2000</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G9" t="s">
         <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>153</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
@@ -2225,7 +2291,7 @@
         <v>1984</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G10" t="s">
         <v>7</v>
@@ -2245,7 +2311,7 @@
         <v>1982</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G11" t="s">
         <v>7</v>
@@ -2265,7 +2331,7 @@
         <v>2008</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G12" t="s">
         <v>7</v>
@@ -2285,7 +2351,7 @@
         <v>1970</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G13" t="s">
         <v>7</v>
@@ -2305,7 +2371,7 @@
         <v>2013</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G14" t="s">
         <v>7</v>
@@ -2325,7 +2391,7 @@
         <v>1969</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G15" t="s">
         <v>7</v>
@@ -2345,13 +2411,13 @@
         <v>1978</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>2</v>
       </c>
@@ -2365,13 +2431,13 @@
         <v>1982</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>2</v>
       </c>
@@ -2385,13 +2451,13 @@
         <v>1987</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>3</v>
       </c>
@@ -2405,19 +2471,22 @@
         <v>1981</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G19" t="s">
         <v>7</v>
       </c>
       <c r="H19" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J19" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>3</v>
       </c>
@@ -2431,13 +2500,13 @@
         <v>2015</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>3</v>
       </c>
@@ -2451,13 +2520,13 @@
         <v>2008</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>3</v>
       </c>
@@ -2471,13 +2540,13 @@
         <v>2010</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>4</v>
       </c>
@@ -2491,19 +2560,22 @@
         <v>2010</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G23" t="s">
         <v>7</v>
       </c>
       <c r="H23" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J23" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>4</v>
       </c>
@@ -2517,13 +2589,13 @@
         <v>1966</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>5</v>
       </c>
@@ -2537,19 +2609,22 @@
         <v>2015</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G25" t="s">
         <v>7</v>
       </c>
       <c r="H25" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J25" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>5</v>
       </c>
@@ -2563,13 +2638,13 @@
         <v>1986</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G26" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>5</v>
       </c>
@@ -2583,13 +2658,13 @@
         <v>1984</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G27" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>6</v>
       </c>
@@ -2603,19 +2678,22 @@
         <v>2024</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G28" t="s">
         <v>7</v>
       </c>
       <c r="H28" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J28" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>6</v>
       </c>
@@ -2629,13 +2707,13 @@
         <v>1987</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>6</v>
       </c>
@@ -2649,13 +2727,13 @@
         <v>1975</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G30" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31">
         <v>6</v>
       </c>
@@ -2669,13 +2747,13 @@
         <v>1981</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G31" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>7</v>
       </c>
@@ -2689,19 +2767,22 @@
         <v>1996</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G32" t="s">
         <v>7</v>
       </c>
       <c r="H32" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J32" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>8</v>
       </c>
@@ -2715,19 +2796,22 @@
         <v>2007</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G33" t="s">
         <v>7</v>
       </c>
       <c r="H33" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J33" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>8</v>
       </c>
@@ -2741,13 +2825,13 @@
         <v>1995</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>8</v>
       </c>
@@ -2761,13 +2845,13 @@
         <v>1984</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B36">
         <v>8</v>
       </c>
@@ -2781,13 +2865,13 @@
         <v>1942</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B37">
         <v>1</v>
       </c>
@@ -2801,19 +2885,22 @@
         <v>1980</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>315</v>
+        <v>516</v>
       </c>
       <c r="G37" t="s">
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J37" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B38">
         <v>1</v>
       </c>
@@ -2827,13 +2914,13 @@
         <v>1985</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>316</v>
+        <v>517</v>
       </c>
       <c r="G38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39">
         <v>1</v>
       </c>
@@ -2847,13 +2934,13 @@
         <v>1983</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>317</v>
+        <v>518</v>
       </c>
       <c r="G39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>1</v>
       </c>
@@ -2867,13 +2954,13 @@
         <v>1984</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G40" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>1</v>
       </c>
@@ -2887,13 +2974,13 @@
         <v>1962</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B42">
         <v>1</v>
       </c>
@@ -2907,13 +2994,13 @@
         <v>2016</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G42" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B43">
         <v>2</v>
       </c>
@@ -2927,19 +3014,22 @@
         <v>1984</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G43" t="s">
         <v>9</v>
       </c>
       <c r="H43" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J43" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B44">
         <v>2</v>
       </c>
@@ -2953,13 +3043,13 @@
         <v>1980</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G44" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B45">
         <v>2</v>
       </c>
@@ -2973,13 +3063,13 @@
         <v>1986</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G45" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B46">
         <v>2</v>
       </c>
@@ -2993,13 +3083,13 @@
         <v>1983</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G46" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B47">
         <v>2</v>
       </c>
@@ -3013,13 +3103,13 @@
         <v>1983</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G47" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B48">
         <v>2</v>
       </c>
@@ -3033,13 +3123,13 @@
         <v>1962</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G48" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49">
         <v>2</v>
       </c>
@@ -3053,13 +3143,13 @@
         <v>1981</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G49" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B50">
         <v>2</v>
       </c>
@@ -3073,13 +3163,13 @@
         <v>2016</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G50" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B51">
         <v>3</v>
       </c>
@@ -3087,25 +3177,28 @@
         <v>37</v>
       </c>
       <c r="D51" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E51">
         <v>1975</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G51" t="s">
         <v>9</v>
       </c>
       <c r="H51" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J51" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B52">
         <v>3</v>
       </c>
@@ -3119,13 +3212,13 @@
         <v>1972</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G52" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B53">
         <v>3</v>
       </c>
@@ -3139,13 +3232,13 @@
         <v>1984</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G53" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B54">
         <v>3</v>
       </c>
@@ -3159,13 +3252,13 @@
         <v>1984</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G54" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B55">
         <v>3</v>
       </c>
@@ -3179,13 +3272,13 @@
         <v>1982</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G55" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B56">
         <v>3</v>
       </c>
@@ -3199,13 +3292,13 @@
         <v>1962</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G56" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B57">
         <v>4</v>
       </c>
@@ -3219,19 +3312,22 @@
         <v>1988</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G57" t="s">
         <v>9</v>
       </c>
       <c r="H57" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J57" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B58">
         <v>4</v>
       </c>
@@ -3245,13 +3341,13 @@
         <v>1983</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G58" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B59">
         <v>4</v>
       </c>
@@ -3265,13 +3361,13 @@
         <v>2011</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B60">
         <v>5</v>
       </c>
@@ -3285,19 +3381,22 @@
         <v>2011</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G60" t="s">
         <v>9</v>
       </c>
       <c r="H60" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J60" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B61">
         <v>5</v>
       </c>
@@ -3311,13 +3410,13 @@
         <v>1992</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B62">
         <v>5</v>
       </c>
@@ -3331,13 +3430,13 @@
         <v>1966</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G62" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B63">
         <v>5</v>
       </c>
@@ -3351,13 +3450,13 @@
         <v>1985</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B64">
         <v>5</v>
       </c>
@@ -3371,13 +3470,13 @@
         <v>1988</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B65">
         <v>5</v>
       </c>
@@ -3391,13 +3490,13 @@
         <v>1984</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B66">
         <v>5</v>
       </c>
@@ -3411,13 +3510,13 @@
         <v>2008</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G66" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B67">
         <v>5</v>
       </c>
@@ -3431,13 +3530,13 @@
         <v>1982</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B68">
         <v>5</v>
       </c>
@@ -3451,13 +3550,13 @@
         <v>1944</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G68" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B69">
         <v>5</v>
       </c>
@@ -3471,13 +3570,13 @@
         <v>1986</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G69" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B70">
         <v>6</v>
       </c>
@@ -3491,19 +3590,22 @@
         <v>1984</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G70" t="s">
         <v>9</v>
       </c>
       <c r="H70" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J70" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B71">
         <v>6</v>
       </c>
@@ -3517,13 +3619,13 @@
         <v>1992</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B72">
         <v>6</v>
       </c>
@@ -3537,13 +3639,13 @@
         <v>1946</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G72" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B73">
         <v>6</v>
       </c>
@@ -3557,13 +3659,13 @@
         <v>1963</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B74">
         <v>6</v>
       </c>
@@ -3577,13 +3679,13 @@
         <v>1984</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G74" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B75">
         <v>7</v>
       </c>
@@ -3597,19 +3699,22 @@
         <v>1984</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G75" t="s">
         <v>9</v>
       </c>
       <c r="H75" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J75" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B76">
         <v>7</v>
       </c>
@@ -3623,13 +3728,13 @@
         <v>1986</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G76" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B77">
         <v>7</v>
       </c>
@@ -3643,13 +3748,13 @@
         <v>1981</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G77" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B78">
         <v>7</v>
       </c>
@@ -3663,13 +3768,13 @@
         <v>1976</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G78" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B79">
         <v>7</v>
       </c>
@@ -3683,13 +3788,13 @@
         <v>1983</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G79" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B80">
         <v>8</v>
       </c>
@@ -3703,19 +3808,22 @@
         <v>1962</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G80" t="s">
         <v>9</v>
       </c>
       <c r="H80" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B81">
         <v>8</v>
       </c>
@@ -3729,13 +3837,13 @@
         <v>1983</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G81" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B82">
         <v>9</v>
       </c>
@@ -3749,19 +3857,22 @@
         <v>1974</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G82" t="s">
         <v>9</v>
       </c>
       <c r="H82" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J82" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B83">
         <v>9</v>
       </c>
@@ -3775,13 +3886,13 @@
         <v>1983</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G83" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B84">
         <v>9</v>
       </c>
@@ -3795,13 +3906,13 @@
         <v>1984</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G84" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B85">
         <v>9</v>
       </c>
@@ -3815,13 +3926,13 @@
         <v>1957</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G85" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B86">
         <v>9</v>
       </c>
@@ -3835,13 +3946,13 @@
         <v>1983</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G86" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B87">
         <v>9</v>
       </c>
@@ -3855,13 +3966,13 @@
         <v>1981</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G87" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B88">
         <v>9</v>
       </c>
@@ -3875,13 +3986,13 @@
         <v>1983</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G88" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B89">
         <v>9</v>
       </c>
@@ -3895,13 +4006,13 @@
         <v>1983</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G89" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B90">
         <v>1</v>
       </c>
@@ -3915,19 +4026,22 @@
         <v>1985</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G90" t="s">
         <v>193</v>
       </c>
       <c r="H90" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="J90" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B91">
         <v>1</v>
       </c>
@@ -3941,13 +4055,13 @@
         <v>1969</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G91" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B92">
         <v>1</v>
       </c>
@@ -3961,13 +4075,13 @@
         <v>2005</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G92" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B93">
         <v>1</v>
       </c>
@@ -3981,13 +4095,13 @@
         <v>1970</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G93" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B94">
         <v>1</v>
       </c>
@@ -4001,13 +4115,13 @@
         <v>1983</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G94" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B95">
         <v>1</v>
       </c>
@@ -4015,19 +4129,19 @@
         <v>203</v>
       </c>
       <c r="D95" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E95">
         <v>1981</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G95" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B96">
         <v>1</v>
       </c>
@@ -4041,7 +4155,7 @@
         <v>1978</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G96" t="s">
         <v>193</v>
@@ -4061,7 +4175,7 @@
         <v>1982</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G97" t="s">
         <v>193</v>
@@ -4081,7 +4195,7 @@
         <v>1962</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G98" t="s">
         <v>193</v>
@@ -4101,7 +4215,7 @@
         <v>1978</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="G99" t="s">
         <v>193</v>
@@ -4121,7 +4235,7 @@
         <v>1984</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G100" t="s">
         <v>193</v>
@@ -4141,7 +4255,7 @@
         <v>1986</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G101" t="s">
         <v>193</v>
@@ -4161,7 +4275,7 @@
         <v>2011</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G102" t="s">
         <v>193</v>
@@ -4181,16 +4295,19 @@
         <v>1982</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="G103" t="s">
         <v>193</v>
       </c>
       <c r="H103" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>286</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.35">
@@ -4207,7 +4324,7 @@
         <v>1983</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G104" t="s">
         <v>193</v>
@@ -4227,7 +4344,7 @@
         <v>1983</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G105" t="s">
         <v>193</v>
@@ -4247,7 +4364,7 @@
         <v>1984</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G106" t="s">
         <v>193</v>
@@ -4267,7 +4384,7 @@
         <v>2016</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="G107" t="s">
         <v>193</v>
@@ -4287,7 +4404,7 @@
         <v>1977</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G108" t="s">
         <v>193</v>
@@ -4307,18 +4424,20 @@
         <v>1984</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G109" t="s">
         <v>193</v>
       </c>
       <c r="H109" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J109" s="2"/>
+      <c r="J109" s="2" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B110">
@@ -4334,7 +4453,7 @@
         <v>2016</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G110" t="s">
         <v>193</v>
@@ -4354,7 +4473,7 @@
         <v>1984</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G111" t="s">
         <v>193</v>
@@ -4374,7 +4493,7 @@
         <v>1982</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="G112" t="s">
         <v>193</v>
@@ -4394,7 +4513,7 @@
         <v>2011</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G113" t="s">
         <v>193</v>
@@ -4414,7 +4533,7 @@
         <v>1984</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="G114" t="s">
         <v>193</v>
@@ -4434,7 +4553,7 @@
         <v>1985</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G115" t="s">
         <v>193</v>
@@ -4454,7 +4573,7 @@
         <v>2008</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G116" t="s">
         <v>193</v>
@@ -4474,7 +4593,7 @@
         <v>1984</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G117" t="s">
         <v>193</v>
@@ -4494,7 +4613,7 @@
         <v>1961</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="G118" t="s">
         <v>193</v>
@@ -4514,7 +4633,7 @@
         <v>1971</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="G119" t="s">
         <v>193</v>
@@ -4534,19 +4653,19 @@
         <v>1939</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G120" t="s">
         <v>193</v>
       </c>
       <c r="H120" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>218</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.35">
@@ -4563,19 +4682,19 @@
         <v>1998</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="G121" t="s">
         <v>193</v>
       </c>
       <c r="H121" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>219</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.35">
@@ -4592,7 +4711,7 @@
         <v>1983</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G122" t="s">
         <v>193</v>
@@ -4612,7 +4731,7 @@
         <v>1988</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="G123" t="s">
         <v>193</v>
@@ -4632,7 +4751,7 @@
         <v>2003</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G124" t="s">
         <v>193</v>
@@ -4652,7 +4771,7 @@
         <v>1994</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G125" t="s">
         <v>193</v>
@@ -4672,7 +4791,7 @@
         <v>2018</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G126" t="s">
         <v>193</v>
@@ -4692,19 +4811,19 @@
         <v>1971</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G127" t="s">
         <v>193</v>
       </c>
       <c r="H127" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>220</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.35">
@@ -4721,7 +4840,7 @@
         <v>1920</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G128" t="s">
         <v>193</v>
@@ -4741,7 +4860,7 @@
         <v>1953</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G129" t="s">
         <v>193</v>
@@ -4761,7 +4880,7 @@
         <v>1988</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G130" t="s">
         <v>193</v>
@@ -4781,7 +4900,7 @@
         <v>1988</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G131" t="s">
         <v>193</v>
@@ -4801,7 +4920,7 @@
         <v>1983</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="G132" t="s">
         <v>193</v>
@@ -4821,7 +4940,7 @@
         <v>2013</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G133" t="s">
         <v>193</v>
@@ -4841,7 +4960,7 @@
         <v>1988</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G134" t="s">
         <v>193</v>
@@ -4861,7 +4980,7 @@
         <v>1985</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G135" t="s">
         <v>193</v>
@@ -4881,19 +5000,19 @@
         <v>1986</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G136" t="s">
         <v>193</v>
       </c>
       <c r="H136" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>221</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.35">
@@ -4910,7 +5029,7 @@
         <v>1889</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G137" t="s">
         <v>193</v>
@@ -4930,7 +5049,7 @@
         <v>1990</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G138" t="s">
         <v>193</v>
@@ -4950,7 +5069,7 @@
         <v>2017</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G139" t="s">
         <v>193</v>
@@ -4964,13 +5083,13 @@
         <v>283</v>
       </c>
       <c r="D140" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E140">
         <v>1899</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G140" t="s">
         <v>193</v>
@@ -4981,7 +5100,7 @@
         <v>7</v>
       </c>
       <c r="C141" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D141" t="s">
         <v>295</v>
@@ -4990,7 +5109,7 @@
         <v>2009</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G141" t="s">
         <v>193</v>
@@ -5010,7 +5129,7 @@
         <v>1983</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G142" t="s">
         <v>193</v>
@@ -5030,7 +5149,7 @@
         <v>1985</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G143" t="s">
         <v>193</v>
@@ -5050,7 +5169,7 @@
         <v>1994</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G144" t="s">
         <v>193</v>
@@ -5070,7 +5189,7 @@
         <v>2010</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G145" t="s">
         <v>193</v>
@@ -5090,19 +5209,19 @@
         <v>1987</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G146" t="s">
         <v>193</v>
       </c>
       <c r="H146" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>223</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.35">
@@ -5119,7 +5238,7 @@
         <v>1967</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G147" t="s">
         <v>193</v>
@@ -5139,7 +5258,7 @@
         <v>1974</v>
       </c>
       <c r="F148" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G148" t="s">
         <v>193</v>
@@ -5159,7 +5278,7 @@
         <v>2019</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G149" t="s">
         <v>193</v>
@@ -5179,7 +5298,7 @@
         <v>2011</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G150" t="s">
         <v>193</v>
@@ -5199,7 +5318,7 @@
         <v>1978</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G151" t="s">
         <v>193</v>
@@ -5219,7 +5338,7 @@
         <v>2019</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G152" t="s">
         <v>193</v>
@@ -5227,160 +5346,180 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F37" r:id="rId1" display="https://www.google.com/imgres?q=whip%20it%20song%20devo&amp;imgurl=https%3A%2F%2Fi.scdn.co%2Fimage%2Fab67616d0000b273f4f1f36551dd41c5442c2a2f&amp;imgrefurl=https%3A%2F%2Fopen.spotify.com%2Fintl-es%2Ftrack%2F4sscDOZCkbLSlDqcCgUJnX&amp;docid=oVDtJaAIUHe9CM&amp;tbnid=NE6pXn75oAFC6M&amp;vet=12ahUKEwjnuuLHm7eVAxU9-AIHHaDgB_wQnPAOegQINBAA..i&amp;w=640&amp;h=640&amp;hcb=2&amp;ved=2ahUKEwjnuuLHm7eVAxU9-AIHHaDgB_wQnPAOegQINBAA" xr:uid="{CEABFEC0-7895-4F62-BED5-C9D13E7A5041}"/>
-    <hyperlink ref="F38" r:id="rId2" display="https://www.google.com/imgres?q=Just%20Another%20Day%09Oingo%20Boingo%0D%0Asong&amp;imgurl=https%3A%2F%2Fi.scdn.co%2Fimage%2Fab67616d0000b273117c53d4921791280aad03ba&amp;imgrefurl=https%3A%2F%2Fopen.spotify.com%2Ftrack%2F6w6I3AFRv7tQMmUTgAghUB&amp;docid=vJLhF4tnMRvm-M&amp;tbnid=40E8TCeBLB_VkM&amp;vet=12ahUKEwixtbnWm7eVAxVK-QIHHfh-CH0QnPAOegQINBAA..i&amp;w=630&amp;h=640&amp;hcb=2&amp;ved=2ahUKEwixtbnWm7eVAxVK-QIHHfh-CH0QnPAOegQINBAA" xr:uid="{8BB839B5-2F19-428C-B6BA-02B3906E6EC7}"/>
-    <hyperlink ref="F39" r:id="rId3" display="https://www.google.com/imgres?q=Talking%20In%20Your%20Sleep%09The%20Romantics%0D%0A&amp;imgurl=https%3A%2F%2Fupload.wikimedia.org%2Fwikipedia%2Fen%2F0%2F0a%2FThe_romantics-talking_in_your_sleep_s.jpg&amp;imgrefurl=https%3A%2F%2Fen.wikipedia.org%2Fwiki%2FTalking_in_Your_Sleep_(The_Romantics_song)&amp;docid=9pp60CM4E4S99M&amp;tbnid=TVKJOnLmoOQXaM&amp;vet=12ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA..i&amp;w=315&amp;h=317&amp;hcb=2&amp;ved=2ahUKEwiwq6fnm7eVAxUC_AIHHQCcIUIQnPAOegQIVBAA" xr:uid="{548F9394-8FD7-4E5E-A739-AA20C7B462E3}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{EBEE5C6C-7AE1-46AA-8945-75B2FB1A63D8}"/>
-    <hyperlink ref="F4" r:id="rId5" xr:uid="{8E99786A-9072-4750-9A6C-6559D69DA39A}"/>
-    <hyperlink ref="F5" r:id="rId6" xr:uid="{E389C741-7024-4418-9F09-2C76960AC9E8}"/>
-    <hyperlink ref="F6" r:id="rId7" xr:uid="{D6111C2C-4FEE-4C47-8800-77251E75106D}"/>
-    <hyperlink ref="F7" r:id="rId8" xr:uid="{AEA3E744-2CEB-457D-AD24-B6A533A5C808}"/>
-    <hyperlink ref="F8" r:id="rId9" xr:uid="{9C9B4333-5A87-4680-A85B-816215193AFD}"/>
-    <hyperlink ref="F9" r:id="rId10" xr:uid="{A1CBDBEE-ED89-41AF-885C-E3A5AB9EEE6C}"/>
-    <hyperlink ref="F10" r:id="rId11" xr:uid="{EC1100A9-DC17-47F7-89D1-273634B2F1E4}"/>
-    <hyperlink ref="F11" r:id="rId12" xr:uid="{80392B61-6154-4372-B0B1-BC3B12DD42C9}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{1EA8F47E-42E2-4B89-9C55-95996E94BC69}"/>
-    <hyperlink ref="F13" r:id="rId14" xr:uid="{776710CF-C4B3-4EB6-B12D-371FA51D9C8A}"/>
-    <hyperlink ref="F14" r:id="rId15" xr:uid="{A389CAB8-73B1-41A2-8B9E-D03C2FA0692A}"/>
-    <hyperlink ref="F15" r:id="rId16" xr:uid="{8835943D-AC76-4CE9-86D8-3EC3BE7CC9ED}"/>
-    <hyperlink ref="F16" r:id="rId17" xr:uid="{C94019BC-9807-43B6-A974-A3D3B5F45759}"/>
-    <hyperlink ref="F17" r:id="rId18" xr:uid="{DCCF46BD-AA23-4C33-8075-2398EFBDE54D}"/>
-    <hyperlink ref="F18" r:id="rId19" xr:uid="{092BE224-6EBA-4689-B715-35D2D7200833}"/>
-    <hyperlink ref="F19" r:id="rId20" xr:uid="{1E2B7EDB-5485-4DFA-9FFB-5214B043808B}"/>
-    <hyperlink ref="F20" r:id="rId21" xr:uid="{9CC7FD77-85C5-4532-AC7E-6D64B94A73DA}"/>
-    <hyperlink ref="F21" r:id="rId22" xr:uid="{503607D2-D0F3-4953-A5E0-7F0344CDCAE9}"/>
-    <hyperlink ref="F22" r:id="rId23" xr:uid="{8E5F0418-536B-4FF3-A996-CE1EB8294567}"/>
-    <hyperlink ref="F23" r:id="rId24" xr:uid="{67E7B28B-76EC-4DAB-A28C-52C22340CB79}"/>
-    <hyperlink ref="F24" r:id="rId25" xr:uid="{103330D5-65DD-410E-9423-5170A00048F1}"/>
-    <hyperlink ref="F25" r:id="rId26" xr:uid="{411DB0EC-E527-437B-AF72-3B4D05BC289A}"/>
-    <hyperlink ref="F26" r:id="rId27" xr:uid="{9B276B0E-ABB5-43D0-A22A-5D2057F83E31}"/>
-    <hyperlink ref="F27" r:id="rId28" xr:uid="{E19A0CD3-0EDC-4A4F-A844-F1D03D8823A4}"/>
-    <hyperlink ref="F28" r:id="rId29" xr:uid="{AA103AEB-1054-4A64-8EF7-974C6E4789CD}"/>
-    <hyperlink ref="F29" r:id="rId30" xr:uid="{BF027D9D-2BFB-44CC-9FC5-4DB20C7997BA}"/>
-    <hyperlink ref="F30" r:id="rId31" xr:uid="{5C8E4A2F-AE62-4DB9-970B-8E120C3B4CBA}"/>
-    <hyperlink ref="F31" r:id="rId32" xr:uid="{8711ACB2-7F8B-4071-8FA8-15679174B987}"/>
-    <hyperlink ref="F32" r:id="rId33" xr:uid="{D1E17956-8344-452C-B808-6BFC6BF0285C}"/>
-    <hyperlink ref="F33" r:id="rId34" xr:uid="{54E01A57-0C9C-47DA-9648-1D79AAAD7B70}"/>
-    <hyperlink ref="F34" r:id="rId35" xr:uid="{7D0875F2-4D85-4B8E-BEAA-CA3284A33D88}"/>
-    <hyperlink ref="F35" r:id="rId36" xr:uid="{70DAD2EE-FA95-4BC6-93B7-4C84DD8747B7}"/>
-    <hyperlink ref="F36" r:id="rId37" xr:uid="{AC32B9EF-88B8-4C0A-98BC-CFC4342416E9}"/>
-    <hyperlink ref="F40" r:id="rId38" xr:uid="{9B7E7A00-F04F-4632-9441-02133DD2069A}"/>
-    <hyperlink ref="F41" r:id="rId39" xr:uid="{9E105A04-B7A9-4D80-8AA4-3D8CFFF2C496}"/>
-    <hyperlink ref="F42" r:id="rId40" xr:uid="{7A1E96B4-A984-4381-A54D-C88B6172382D}"/>
-    <hyperlink ref="F43" r:id="rId41" xr:uid="{CBC05CE3-4B62-44F0-B063-2574BCB33593}"/>
-    <hyperlink ref="F44" r:id="rId42" xr:uid="{C8BE8B1E-E573-40AF-8628-9BAA53CE7BF9}"/>
-    <hyperlink ref="F45" r:id="rId43" xr:uid="{9A396326-06E9-40BE-8577-73DF57B60957}"/>
-    <hyperlink ref="F46" r:id="rId44" xr:uid="{5F30CD71-8849-4815-B084-861DDB31A00E}"/>
-    <hyperlink ref="F47" r:id="rId45" xr:uid="{164211E1-D250-4210-B3B4-21CD055EB93D}"/>
-    <hyperlink ref="F48" r:id="rId46" xr:uid="{37416CE2-DCC6-4A0B-B613-0BFD7CA121A0}"/>
-    <hyperlink ref="F49" r:id="rId47" xr:uid="{65706E76-0698-4A71-8390-F4996B8235F1}"/>
-    <hyperlink ref="F50" r:id="rId48" xr:uid="{F960FAED-6B14-454F-AC20-81FEB88BDF87}"/>
-    <hyperlink ref="F51" r:id="rId49" xr:uid="{4B736073-86A5-4921-BE5B-E6D8A077EA0D}"/>
-    <hyperlink ref="F52" r:id="rId50" xr:uid="{486E5C1E-77FF-443E-B757-3105017F1489}"/>
-    <hyperlink ref="F53" r:id="rId51" xr:uid="{A9E9277D-36BE-42E2-BE44-063D425DE1BF}"/>
-    <hyperlink ref="F54" r:id="rId52" xr:uid="{8C6D7D85-F8B3-4CC9-93DA-17BDCBC58E65}"/>
-    <hyperlink ref="F55" r:id="rId53" xr:uid="{09C00082-4016-4764-BD7F-129F474D6D98}"/>
-    <hyperlink ref="F56" r:id="rId54" xr:uid="{01F04D16-6013-436A-9340-AE07AB3FBDF2}"/>
-    <hyperlink ref="F57" r:id="rId55" xr:uid="{C0015A97-1B83-4AB5-9A76-52566F5EB733}"/>
-    <hyperlink ref="F58" r:id="rId56" xr:uid="{DF9A635C-126B-4B81-BD14-4E5BDE57D360}"/>
-    <hyperlink ref="F59" r:id="rId57" xr:uid="{70FDC6F1-E3D1-46EC-A3F7-57E7E4DD02BE}"/>
-    <hyperlink ref="F60" r:id="rId58" xr:uid="{AF2CB4DB-0F63-4EFA-908F-049475EFA9E7}"/>
-    <hyperlink ref="F61" r:id="rId59" xr:uid="{A2C1036A-F31C-4B28-AA15-FC5BC296D308}"/>
-    <hyperlink ref="F62" r:id="rId60" xr:uid="{F1C2A288-6AB7-4D6C-9DF4-2F81136001BD}"/>
-    <hyperlink ref="F63" r:id="rId61" xr:uid="{980F9DDA-5D33-469E-B032-9E24D7C1B2E0}"/>
-    <hyperlink ref="F64" r:id="rId62" xr:uid="{538A9B5F-8314-4735-9930-B2ED398D3CD6}"/>
-    <hyperlink ref="F65" r:id="rId63" xr:uid="{4E12FE13-4C11-4998-9366-8202DF690B80}"/>
-    <hyperlink ref="F66" r:id="rId64" xr:uid="{B7B17A4A-68ED-4D4B-A5D1-BB12074BA9DC}"/>
-    <hyperlink ref="F67" r:id="rId65" xr:uid="{4BFD0EEB-7470-46EC-AC56-0BFBAD347B3B}"/>
-    <hyperlink ref="F68" r:id="rId66" xr:uid="{5C3BD910-6A90-41E1-9965-D7888B48A918}"/>
-    <hyperlink ref="F69" r:id="rId67" xr:uid="{D1E4D1EA-DECE-4B20-9801-C74F2F7664F2}"/>
-    <hyperlink ref="F70" r:id="rId68" xr:uid="{C79B78AE-8F3C-44C1-9E11-45E5112D89A4}"/>
-    <hyperlink ref="F71" r:id="rId69" xr:uid="{3E12B6B4-DA38-4480-A22C-370C8F2F8F0B}"/>
-    <hyperlink ref="F72" r:id="rId70" xr:uid="{73687896-4DBD-4801-AB53-94749802083B}"/>
-    <hyperlink ref="F73" r:id="rId71" xr:uid="{CDA99111-643A-447C-A27B-1B44951203B8}"/>
-    <hyperlink ref="F74" r:id="rId72" xr:uid="{12A88964-AA18-4EBE-9452-CF60B585E9CA}"/>
-    <hyperlink ref="F75" r:id="rId73" xr:uid="{B19667DD-32E8-40E0-A3F6-C22283F24AFC}"/>
-    <hyperlink ref="F76" r:id="rId74" xr:uid="{1FA82F97-C56B-4B4E-B3E5-CBDAC47A84BC}"/>
-    <hyperlink ref="F77" r:id="rId75" xr:uid="{A2587DCF-2761-4AE4-97B9-A4180226846F}"/>
-    <hyperlink ref="F78" r:id="rId76" xr:uid="{D3AE1623-0079-44C6-82CE-7A066EBE1E1D}"/>
-    <hyperlink ref="F79" r:id="rId77" xr:uid="{B0C88619-9451-42AA-A31E-586750F39727}"/>
-    <hyperlink ref="F80" r:id="rId78" xr:uid="{96F42F96-7BCF-405E-A95E-E229F3807090}"/>
-    <hyperlink ref="F81" r:id="rId79" xr:uid="{07A399C2-C32C-4E8E-AE29-85A548019F11}"/>
-    <hyperlink ref="F82" r:id="rId80" xr:uid="{672178A5-0536-4449-91A0-AADCB5150688}"/>
-    <hyperlink ref="F83" r:id="rId81" xr:uid="{E17F8816-1F9E-4CF4-B6C8-B8BE6B73C861}"/>
-    <hyperlink ref="F84" r:id="rId82" xr:uid="{4D074580-7E0A-4CB4-AF7A-5D22387A2DEF}"/>
-    <hyperlink ref="F85" r:id="rId83" xr:uid="{F50D187A-28F9-4FB3-96C5-9F1A0D4B3C0A}"/>
-    <hyperlink ref="F86" r:id="rId84" xr:uid="{BD92A685-7644-4EAE-A71C-6282DDF46E36}"/>
-    <hyperlink ref="F87" r:id="rId85" xr:uid="{BCA2468D-1173-4107-BFC1-D6222898C756}"/>
-    <hyperlink ref="F88" r:id="rId86" xr:uid="{B0B7B318-EDA2-418D-AF9E-E708AA943AD8}"/>
-    <hyperlink ref="F89" r:id="rId87" xr:uid="{CA190611-3FEA-4B3C-BDEA-E894BA7E0B51}"/>
-    <hyperlink ref="F90" r:id="rId88" xr:uid="{EE0AD7DB-964D-46E8-AC21-3C625DFB4892}"/>
-    <hyperlink ref="F91" r:id="rId89" xr:uid="{4F86780C-AC81-4798-89B7-7BBEF3BA5125}"/>
-    <hyperlink ref="F92" r:id="rId90" xr:uid="{5AA9B59F-2554-41E8-8E84-275A682D8356}"/>
-    <hyperlink ref="F93" r:id="rId91" xr:uid="{5399AE5C-7E51-40E3-8730-0E0DFE0EDAA3}"/>
-    <hyperlink ref="F94" r:id="rId92" xr:uid="{213CB07D-6520-4678-A8C3-F3FE331A2FE4}"/>
-    <hyperlink ref="F95" r:id="rId93" xr:uid="{BE5DBFD0-A4E1-4B6D-B997-195C31C9033F}"/>
-    <hyperlink ref="F96" r:id="rId94" xr:uid="{2D2FD5DC-AA4B-437C-864C-914726CE0B19}"/>
-    <hyperlink ref="F97" r:id="rId95" xr:uid="{9B7DBB46-388A-4A6E-876B-245B033C593C}"/>
-    <hyperlink ref="F98" r:id="rId96" xr:uid="{E64AE5F5-ED9E-4F89-80D3-36B2ADCA765A}"/>
-    <hyperlink ref="F99" r:id="rId97" xr:uid="{FAADB430-0C4D-462C-A5E0-327E69331ECD}"/>
-    <hyperlink ref="F100" r:id="rId98" xr:uid="{E4F11F6B-F74C-41BB-BA4A-726EF9BFF135}"/>
-    <hyperlink ref="F101" r:id="rId99" xr:uid="{963E28A5-4A36-4DA7-A39E-4EB6A4972B5B}"/>
-    <hyperlink ref="F102" r:id="rId100" xr:uid="{E53FAA3F-14A0-4FFC-9041-A63681EA3AAD}"/>
-    <hyperlink ref="F103" r:id="rId101" xr:uid="{BE7F5E36-A70D-4969-BD9A-4969EE31ECD2}"/>
-    <hyperlink ref="F104" r:id="rId102" xr:uid="{D094EF61-2138-46F1-8129-219CF6574411}"/>
-    <hyperlink ref="F105" r:id="rId103" xr:uid="{2BDE5563-26C2-4BCD-8728-D13E536DFDE8}"/>
-    <hyperlink ref="F106" r:id="rId104" xr:uid="{BE46DC8F-C1C3-4C30-9CCD-596FD61880DF}"/>
-    <hyperlink ref="F107" r:id="rId105" xr:uid="{B04DEA0D-650E-45A8-97A8-8A239FB454E8}"/>
-    <hyperlink ref="F108" r:id="rId106" xr:uid="{C7AB48FA-187E-4EC7-BBC0-C34C48E804B6}"/>
-    <hyperlink ref="F109" r:id="rId107" xr:uid="{12B5E0F7-71D4-44F2-ABBC-5CD1B1E15630}"/>
-    <hyperlink ref="F110" r:id="rId108" xr:uid="{AF7460AD-2169-4389-9102-CC9996D382C0}"/>
-    <hyperlink ref="F111" r:id="rId109" xr:uid="{D65C6847-A23D-458D-8720-D0FEE3F10F86}"/>
-    <hyperlink ref="F112" r:id="rId110" xr:uid="{C1F6F441-ECE2-46B7-BC01-27B962C4AB16}"/>
-    <hyperlink ref="F113" r:id="rId111" xr:uid="{C966B0A2-541E-4E32-AF5F-DBC955C1DB06}"/>
-    <hyperlink ref="F114" r:id="rId112" xr:uid="{5E6F5E0F-3CD7-483E-A6EF-F2101F8078B3}"/>
-    <hyperlink ref="F115" r:id="rId113" xr:uid="{08215017-D939-4531-87ED-9E8425D34601}"/>
-    <hyperlink ref="F116" r:id="rId114" xr:uid="{C2445B34-A362-448C-89D0-B78ABDA67E46}"/>
-    <hyperlink ref="F117" r:id="rId115" xr:uid="{2F22D7CD-C26B-4E97-87B2-D69CCE84F53B}"/>
-    <hyperlink ref="F118" r:id="rId116" xr:uid="{C0E1AECB-DF64-4EEB-BDD8-1F0BAD6C81B5}"/>
-    <hyperlink ref="F119" r:id="rId117" xr:uid="{03DD02FA-B4B9-46AB-91A0-E76930C094A8}"/>
-    <hyperlink ref="F120" r:id="rId118" xr:uid="{3ECDC44E-949F-42C0-B986-4C558423CBBE}"/>
-    <hyperlink ref="F121" r:id="rId119" xr:uid="{A0851054-AF48-43AF-BA33-D081F9C766B9}"/>
-    <hyperlink ref="F122" r:id="rId120" xr:uid="{BEBB832A-C39C-4F79-B145-9B36E12C3CB1}"/>
-    <hyperlink ref="F123" r:id="rId121" xr:uid="{E4FDC80C-8C6D-4C03-B8DB-938614A67889}"/>
-    <hyperlink ref="F124" r:id="rId122" xr:uid="{E25353C4-311A-4A6C-9B26-00C1E48C823B}"/>
-    <hyperlink ref="F125" r:id="rId123" xr:uid="{051E01FE-D93B-491B-AC40-D7D8ED72239E}"/>
-    <hyperlink ref="F126" r:id="rId124" xr:uid="{3603EB80-64EC-4629-A1B4-7AE6ADCC7114}"/>
-    <hyperlink ref="F127" r:id="rId125" xr:uid="{03E3762D-87C1-41B4-921F-7361AFAFBF2F}"/>
-    <hyperlink ref="F128" r:id="rId126" xr:uid="{A4B68288-E639-49F4-993C-29EAA4072A71}"/>
-    <hyperlink ref="F129" r:id="rId127" xr:uid="{C9D31F1C-A8CB-4799-A2A4-68E0945ABAAE}"/>
-    <hyperlink ref="F130" r:id="rId128" xr:uid="{FD353834-3E91-4CBB-A6C4-8B495E23D124}"/>
-    <hyperlink ref="F131" r:id="rId129" xr:uid="{7B0E69D1-6FDF-4BBA-9AA4-C5A6BF27C928}"/>
-    <hyperlink ref="F132" r:id="rId130" xr:uid="{9EBB9C49-BCBE-4EB8-BDB2-643167D609F8}"/>
-    <hyperlink ref="F133" r:id="rId131" xr:uid="{4DD7AB03-5DF6-4762-92E4-60B9EC6085F5}"/>
-    <hyperlink ref="F134" r:id="rId132" xr:uid="{ED8F2DB2-2B42-4883-9309-09AED4183D23}"/>
-    <hyperlink ref="F135" r:id="rId133" xr:uid="{A9AE5049-EC61-41A6-8788-F4B50355FA8D}"/>
-    <hyperlink ref="F136" r:id="rId134" xr:uid="{667027A3-4CF9-4B8A-A3FE-993C565D0F4C}"/>
-    <hyperlink ref="F137" r:id="rId135" xr:uid="{F25C4A50-CBE2-4E7A-859B-2FD1E573F254}"/>
-    <hyperlink ref="F138" r:id="rId136" xr:uid="{75FE179B-AF3B-4843-95BD-3EED8C14F364}"/>
-    <hyperlink ref="F139" r:id="rId137" xr:uid="{BE8AAB48-8749-40A3-AC68-AF790396A474}"/>
-    <hyperlink ref="F140" r:id="rId138" xr:uid="{71DD0714-9997-4016-9594-D53081FBA758}"/>
-    <hyperlink ref="F141" r:id="rId139" xr:uid="{7D4236B4-C6D2-4D9E-87D3-21CE2879F2B7}"/>
-    <hyperlink ref="F142" r:id="rId140" xr:uid="{AB78A0F2-0618-4D77-A42C-F41159E73520}"/>
-    <hyperlink ref="F143" r:id="rId141" xr:uid="{951D3B33-2808-4219-B8C0-6A78623E5AA1}"/>
-    <hyperlink ref="F144" r:id="rId142" xr:uid="{A9CE9CF3-160D-4B9F-B8BE-5E531859664C}"/>
-    <hyperlink ref="F145" r:id="rId143" xr:uid="{7A3502EB-AF45-4EE3-88E8-17228934C08E}"/>
-    <hyperlink ref="F146" r:id="rId144" xr:uid="{F89DC979-7339-4628-903D-928FCCCADEE5}"/>
-    <hyperlink ref="F147" r:id="rId145" xr:uid="{D2CACEA3-B167-4FE3-A994-3AD59A20A9A7}"/>
-    <hyperlink ref="F149" r:id="rId146" xr:uid="{22AC07A4-5F12-41FA-8FA8-D4F00424A9EC}"/>
-    <hyperlink ref="F150" r:id="rId147" xr:uid="{357908BA-3A52-4D80-B702-8F516D20FE4D}"/>
-    <hyperlink ref="F151" r:id="rId148" xr:uid="{30560881-6166-4C8F-84C3-DB257B037A99}"/>
-    <hyperlink ref="F152" r:id="rId149" xr:uid="{40EBB7C0-3D94-4005-BF13-1726CA98A382}"/>
-    <hyperlink ref="J146" r:id="rId150" xr:uid="{A0AAB73C-0E04-4F9C-A00E-1ECD18CD39DB}"/>
-    <hyperlink ref="J136" r:id="rId151" xr:uid="{208E28B7-2A86-42C6-8126-3F2AE9DA2E16}"/>
-    <hyperlink ref="J127" r:id="rId152" xr:uid="{3F6E69B2-FCE2-4047-A391-15513C571279}"/>
-    <hyperlink ref="J121" r:id="rId153" xr:uid="{E650C24A-5A75-4844-AD6D-D5FCDBCA2FD3}"/>
-    <hyperlink ref="J120" r:id="rId154" xr:uid="{53678A32-886B-4B53-B546-0001E24DF42B}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{EBEE5C6C-7AE1-46AA-8945-75B2FB1A63D8}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{8E99786A-9072-4750-9A6C-6559D69DA39A}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{E389C741-7024-4418-9F09-2C76960AC9E8}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{D6111C2C-4FEE-4C47-8800-77251E75106D}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{AEA3E744-2CEB-457D-AD24-B6A533A5C808}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{9C9B4333-5A87-4680-A85B-816215193AFD}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{A1CBDBEE-ED89-41AF-885C-E3A5AB9EEE6C}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{EC1100A9-DC17-47F7-89D1-273634B2F1E4}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{80392B61-6154-4372-B0B1-BC3B12DD42C9}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{1EA8F47E-42E2-4B89-9C55-95996E94BC69}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{776710CF-C4B3-4EB6-B12D-371FA51D9C8A}"/>
+    <hyperlink ref="F14" r:id="rId12" xr:uid="{A389CAB8-73B1-41A2-8B9E-D03C2FA0692A}"/>
+    <hyperlink ref="F15" r:id="rId13" xr:uid="{8835943D-AC76-4CE9-86D8-3EC3BE7CC9ED}"/>
+    <hyperlink ref="F16" r:id="rId14" xr:uid="{C94019BC-9807-43B6-A974-A3D3B5F45759}"/>
+    <hyperlink ref="F17" r:id="rId15" xr:uid="{DCCF46BD-AA23-4C33-8075-2398EFBDE54D}"/>
+    <hyperlink ref="F18" r:id="rId16" xr:uid="{092BE224-6EBA-4689-B715-35D2D7200833}"/>
+    <hyperlink ref="F19" r:id="rId17" xr:uid="{1E2B7EDB-5485-4DFA-9FFB-5214B043808B}"/>
+    <hyperlink ref="F20" r:id="rId18" xr:uid="{9CC7FD77-85C5-4532-AC7E-6D64B94A73DA}"/>
+    <hyperlink ref="F21" r:id="rId19" xr:uid="{503607D2-D0F3-4953-A5E0-7F0344CDCAE9}"/>
+    <hyperlink ref="F22" r:id="rId20" xr:uid="{8E5F0418-536B-4FF3-A996-CE1EB8294567}"/>
+    <hyperlink ref="F23" r:id="rId21" xr:uid="{67E7B28B-76EC-4DAB-A28C-52C22340CB79}"/>
+    <hyperlink ref="F24" r:id="rId22" xr:uid="{103330D5-65DD-410E-9423-5170A00048F1}"/>
+    <hyperlink ref="F25" r:id="rId23" xr:uid="{411DB0EC-E527-437B-AF72-3B4D05BC289A}"/>
+    <hyperlink ref="F26" r:id="rId24" xr:uid="{9B276B0E-ABB5-43D0-A22A-5D2057F83E31}"/>
+    <hyperlink ref="F27" r:id="rId25" xr:uid="{E19A0CD3-0EDC-4A4F-A844-F1D03D8823A4}"/>
+    <hyperlink ref="F28" r:id="rId26" xr:uid="{AA103AEB-1054-4A64-8EF7-974C6E4789CD}"/>
+    <hyperlink ref="F29" r:id="rId27" xr:uid="{BF027D9D-2BFB-44CC-9FC5-4DB20C7997BA}"/>
+    <hyperlink ref="F30" r:id="rId28" xr:uid="{5C8E4A2F-AE62-4DB9-970B-8E120C3B4CBA}"/>
+    <hyperlink ref="F31" r:id="rId29" xr:uid="{8711ACB2-7F8B-4071-8FA8-15679174B987}"/>
+    <hyperlink ref="F32" r:id="rId30" xr:uid="{D1E17956-8344-452C-B808-6BFC6BF0285C}"/>
+    <hyperlink ref="F33" r:id="rId31" xr:uid="{54E01A57-0C9C-47DA-9648-1D79AAAD7B70}"/>
+    <hyperlink ref="F34" r:id="rId32" xr:uid="{7D0875F2-4D85-4B8E-BEAA-CA3284A33D88}"/>
+    <hyperlink ref="F35" r:id="rId33" xr:uid="{70DAD2EE-FA95-4BC6-93B7-4C84DD8747B7}"/>
+    <hyperlink ref="F36" r:id="rId34" xr:uid="{AC32B9EF-88B8-4C0A-98BC-CFC4342416E9}"/>
+    <hyperlink ref="F40" r:id="rId35" xr:uid="{9B7E7A00-F04F-4632-9441-02133DD2069A}"/>
+    <hyperlink ref="F41" r:id="rId36" xr:uid="{9E105A04-B7A9-4D80-8AA4-3D8CFFF2C496}"/>
+    <hyperlink ref="F42" r:id="rId37" xr:uid="{7A1E96B4-A984-4381-A54D-C88B6172382D}"/>
+    <hyperlink ref="F43" r:id="rId38" xr:uid="{CBC05CE3-4B62-44F0-B063-2574BCB33593}"/>
+    <hyperlink ref="F44" r:id="rId39" xr:uid="{C8BE8B1E-E573-40AF-8628-9BAA53CE7BF9}"/>
+    <hyperlink ref="F45" r:id="rId40" xr:uid="{9A396326-06E9-40BE-8577-73DF57B60957}"/>
+    <hyperlink ref="F46" r:id="rId41" xr:uid="{5F30CD71-8849-4815-B084-861DDB31A00E}"/>
+    <hyperlink ref="F47" r:id="rId42" xr:uid="{164211E1-D250-4210-B3B4-21CD055EB93D}"/>
+    <hyperlink ref="F48" r:id="rId43" xr:uid="{37416CE2-DCC6-4A0B-B613-0BFD7CA121A0}"/>
+    <hyperlink ref="F49" r:id="rId44" xr:uid="{65706E76-0698-4A71-8390-F4996B8235F1}"/>
+    <hyperlink ref="F50" r:id="rId45" xr:uid="{F960FAED-6B14-454F-AC20-81FEB88BDF87}"/>
+    <hyperlink ref="F51" r:id="rId46" xr:uid="{4B736073-86A5-4921-BE5B-E6D8A077EA0D}"/>
+    <hyperlink ref="F52" r:id="rId47" xr:uid="{486E5C1E-77FF-443E-B757-3105017F1489}"/>
+    <hyperlink ref="F53" r:id="rId48" xr:uid="{A9E9277D-36BE-42E2-BE44-063D425DE1BF}"/>
+    <hyperlink ref="F54" r:id="rId49" xr:uid="{8C6D7D85-F8B3-4CC9-93DA-17BDCBC58E65}"/>
+    <hyperlink ref="F55" r:id="rId50" xr:uid="{09C00082-4016-4764-BD7F-129F474D6D98}"/>
+    <hyperlink ref="F56" r:id="rId51" xr:uid="{01F04D16-6013-436A-9340-AE07AB3FBDF2}"/>
+    <hyperlink ref="F57" r:id="rId52" xr:uid="{C0015A97-1B83-4AB5-9A76-52566F5EB733}"/>
+    <hyperlink ref="F58" r:id="rId53" xr:uid="{DF9A635C-126B-4B81-BD14-4E5BDE57D360}"/>
+    <hyperlink ref="F59" r:id="rId54" xr:uid="{70FDC6F1-E3D1-46EC-A3F7-57E7E4DD02BE}"/>
+    <hyperlink ref="F60" r:id="rId55" xr:uid="{AF2CB4DB-0F63-4EFA-908F-049475EFA9E7}"/>
+    <hyperlink ref="F61" r:id="rId56" xr:uid="{A2C1036A-F31C-4B28-AA15-FC5BC296D308}"/>
+    <hyperlink ref="F62" r:id="rId57" xr:uid="{F1C2A288-6AB7-4D6C-9DF4-2F81136001BD}"/>
+    <hyperlink ref="F63" r:id="rId58" xr:uid="{980F9DDA-5D33-469E-B032-9E24D7C1B2E0}"/>
+    <hyperlink ref="F64" r:id="rId59" xr:uid="{538A9B5F-8314-4735-9930-B2ED398D3CD6}"/>
+    <hyperlink ref="F65" r:id="rId60" xr:uid="{4E12FE13-4C11-4998-9366-8202DF690B80}"/>
+    <hyperlink ref="F66" r:id="rId61" xr:uid="{B7B17A4A-68ED-4D4B-A5D1-BB12074BA9DC}"/>
+    <hyperlink ref="F67" r:id="rId62" xr:uid="{4BFD0EEB-7470-46EC-AC56-0BFBAD347B3B}"/>
+    <hyperlink ref="F68" r:id="rId63" xr:uid="{5C3BD910-6A90-41E1-9965-D7888B48A918}"/>
+    <hyperlink ref="F69" r:id="rId64" xr:uid="{D1E4D1EA-DECE-4B20-9801-C74F2F7664F2}"/>
+    <hyperlink ref="F70" r:id="rId65" xr:uid="{C79B78AE-8F3C-44C1-9E11-45E5112D89A4}"/>
+    <hyperlink ref="F71" r:id="rId66" xr:uid="{3E12B6B4-DA38-4480-A22C-370C8F2F8F0B}"/>
+    <hyperlink ref="F72" r:id="rId67" xr:uid="{73687896-4DBD-4801-AB53-94749802083B}"/>
+    <hyperlink ref="F73" r:id="rId68" xr:uid="{CDA99111-643A-447C-A27B-1B44951203B8}"/>
+    <hyperlink ref="F74" r:id="rId69" xr:uid="{12A88964-AA18-4EBE-9452-CF60B585E9CA}"/>
+    <hyperlink ref="F75" r:id="rId70" xr:uid="{B19667DD-32E8-40E0-A3F6-C22283F24AFC}"/>
+    <hyperlink ref="F76" r:id="rId71" xr:uid="{1FA82F97-C56B-4B4E-B3E5-CBDAC47A84BC}"/>
+    <hyperlink ref="F77" r:id="rId72" xr:uid="{A2587DCF-2761-4AE4-97B9-A4180226846F}"/>
+    <hyperlink ref="F78" r:id="rId73" xr:uid="{D3AE1623-0079-44C6-82CE-7A066EBE1E1D}"/>
+    <hyperlink ref="F79" r:id="rId74" xr:uid="{B0C88619-9451-42AA-A31E-586750F39727}"/>
+    <hyperlink ref="F80" r:id="rId75" xr:uid="{96F42F96-7BCF-405E-A95E-E229F3807090}"/>
+    <hyperlink ref="F81" r:id="rId76" xr:uid="{07A399C2-C32C-4E8E-AE29-85A548019F11}"/>
+    <hyperlink ref="F82" r:id="rId77" xr:uid="{672178A5-0536-4449-91A0-AADCB5150688}"/>
+    <hyperlink ref="F83" r:id="rId78" xr:uid="{E17F8816-1F9E-4CF4-B6C8-B8BE6B73C861}"/>
+    <hyperlink ref="F84" r:id="rId79" xr:uid="{4D074580-7E0A-4CB4-AF7A-5D22387A2DEF}"/>
+    <hyperlink ref="F85" r:id="rId80" xr:uid="{F50D187A-28F9-4FB3-96C5-9F1A0D4B3C0A}"/>
+    <hyperlink ref="F86" r:id="rId81" xr:uid="{BD92A685-7644-4EAE-A71C-6282DDF46E36}"/>
+    <hyperlink ref="F87" r:id="rId82" xr:uid="{BCA2468D-1173-4107-BFC1-D6222898C756}"/>
+    <hyperlink ref="F88" r:id="rId83" xr:uid="{B0B7B318-EDA2-418D-AF9E-E708AA943AD8}"/>
+    <hyperlink ref="F89" r:id="rId84" xr:uid="{CA190611-3FEA-4B3C-BDEA-E894BA7E0B51}"/>
+    <hyperlink ref="F90" r:id="rId85" xr:uid="{EE0AD7DB-964D-46E8-AC21-3C625DFB4892}"/>
+    <hyperlink ref="F91" r:id="rId86" xr:uid="{4F86780C-AC81-4798-89B7-7BBEF3BA5125}"/>
+    <hyperlink ref="F92" r:id="rId87" xr:uid="{5AA9B59F-2554-41E8-8E84-275A682D8356}"/>
+    <hyperlink ref="F93" r:id="rId88" xr:uid="{5399AE5C-7E51-40E3-8730-0E0DFE0EDAA3}"/>
+    <hyperlink ref="F94" r:id="rId89" xr:uid="{213CB07D-6520-4678-A8C3-F3FE331A2FE4}"/>
+    <hyperlink ref="F95" r:id="rId90" xr:uid="{BE5DBFD0-A4E1-4B6D-B997-195C31C9033F}"/>
+    <hyperlink ref="F96" r:id="rId91" xr:uid="{2D2FD5DC-AA4B-437C-864C-914726CE0B19}"/>
+    <hyperlink ref="F97" r:id="rId92" xr:uid="{9B7DBB46-388A-4A6E-876B-245B033C593C}"/>
+    <hyperlink ref="F98" r:id="rId93" xr:uid="{E64AE5F5-ED9E-4F89-80D3-36B2ADCA765A}"/>
+    <hyperlink ref="F99" r:id="rId94" xr:uid="{FAADB430-0C4D-462C-A5E0-327E69331ECD}"/>
+    <hyperlink ref="F100" r:id="rId95" xr:uid="{E4F11F6B-F74C-41BB-BA4A-726EF9BFF135}"/>
+    <hyperlink ref="F101" r:id="rId96" xr:uid="{963E28A5-4A36-4DA7-A39E-4EB6A4972B5B}"/>
+    <hyperlink ref="F102" r:id="rId97" xr:uid="{E53FAA3F-14A0-4FFC-9041-A63681EA3AAD}"/>
+    <hyperlink ref="F103" r:id="rId98" xr:uid="{BE7F5E36-A70D-4969-BD9A-4969EE31ECD2}"/>
+    <hyperlink ref="F104" r:id="rId99" xr:uid="{D094EF61-2138-46F1-8129-219CF6574411}"/>
+    <hyperlink ref="F105" r:id="rId100" xr:uid="{2BDE5563-26C2-4BCD-8728-D13E536DFDE8}"/>
+    <hyperlink ref="F106" r:id="rId101" xr:uid="{BE46DC8F-C1C3-4C30-9CCD-596FD61880DF}"/>
+    <hyperlink ref="F107" r:id="rId102" xr:uid="{B04DEA0D-650E-45A8-97A8-8A239FB454E8}"/>
+    <hyperlink ref="F108" r:id="rId103" xr:uid="{C7AB48FA-187E-4EC7-BBC0-C34C48E804B6}"/>
+    <hyperlink ref="F109" r:id="rId104" xr:uid="{12B5E0F7-71D4-44F2-ABBC-5CD1B1E15630}"/>
+    <hyperlink ref="F110" r:id="rId105" xr:uid="{AF7460AD-2169-4389-9102-CC9996D382C0}"/>
+    <hyperlink ref="F111" r:id="rId106" xr:uid="{D65C6847-A23D-458D-8720-D0FEE3F10F86}"/>
+    <hyperlink ref="F112" r:id="rId107" xr:uid="{C1F6F441-ECE2-46B7-BC01-27B962C4AB16}"/>
+    <hyperlink ref="F113" r:id="rId108" xr:uid="{C966B0A2-541E-4E32-AF5F-DBC955C1DB06}"/>
+    <hyperlink ref="F114" r:id="rId109" xr:uid="{5E6F5E0F-3CD7-483E-A6EF-F2101F8078B3}"/>
+    <hyperlink ref="F115" r:id="rId110" xr:uid="{08215017-D939-4531-87ED-9E8425D34601}"/>
+    <hyperlink ref="F116" r:id="rId111" xr:uid="{C2445B34-A362-448C-89D0-B78ABDA67E46}"/>
+    <hyperlink ref="F117" r:id="rId112" xr:uid="{2F22D7CD-C26B-4E97-87B2-D69CCE84F53B}"/>
+    <hyperlink ref="F118" r:id="rId113" xr:uid="{C0E1AECB-DF64-4EEB-BDD8-1F0BAD6C81B5}"/>
+    <hyperlink ref="F119" r:id="rId114" xr:uid="{03DD02FA-B4B9-46AB-91A0-E76930C094A8}"/>
+    <hyperlink ref="F120" r:id="rId115" xr:uid="{3ECDC44E-949F-42C0-B986-4C558423CBBE}"/>
+    <hyperlink ref="F121" r:id="rId116" xr:uid="{A0851054-AF48-43AF-BA33-D081F9C766B9}"/>
+    <hyperlink ref="F122" r:id="rId117" xr:uid="{BEBB832A-C39C-4F79-B145-9B36E12C3CB1}"/>
+    <hyperlink ref="F123" r:id="rId118" xr:uid="{E4FDC80C-8C6D-4C03-B8DB-938614A67889}"/>
+    <hyperlink ref="F124" r:id="rId119" xr:uid="{E25353C4-311A-4A6C-9B26-00C1E48C823B}"/>
+    <hyperlink ref="F125" r:id="rId120" xr:uid="{051E01FE-D93B-491B-AC40-D7D8ED72239E}"/>
+    <hyperlink ref="F126" r:id="rId121" xr:uid="{3603EB80-64EC-4629-A1B4-7AE6ADCC7114}"/>
+    <hyperlink ref="F127" r:id="rId122" xr:uid="{03E3762D-87C1-41B4-921F-7361AFAFBF2F}"/>
+    <hyperlink ref="F128" r:id="rId123" xr:uid="{A4B68288-E639-49F4-993C-29EAA4072A71}"/>
+    <hyperlink ref="F129" r:id="rId124" xr:uid="{C9D31F1C-A8CB-4799-A2A4-68E0945ABAAE}"/>
+    <hyperlink ref="F130" r:id="rId125" xr:uid="{FD353834-3E91-4CBB-A6C4-8B495E23D124}"/>
+    <hyperlink ref="F131" r:id="rId126" xr:uid="{7B0E69D1-6FDF-4BBA-9AA4-C5A6BF27C928}"/>
+    <hyperlink ref="F132" r:id="rId127" xr:uid="{9EBB9C49-BCBE-4EB8-BDB2-643167D609F8}"/>
+    <hyperlink ref="F133" r:id="rId128" xr:uid="{4DD7AB03-5DF6-4762-92E4-60B9EC6085F5}"/>
+    <hyperlink ref="F134" r:id="rId129" xr:uid="{ED8F2DB2-2B42-4883-9309-09AED4183D23}"/>
+    <hyperlink ref="F135" r:id="rId130" xr:uid="{A9AE5049-EC61-41A6-8788-F4B50355FA8D}"/>
+    <hyperlink ref="F136" r:id="rId131" xr:uid="{667027A3-4CF9-4B8A-A3FE-993C565D0F4C}"/>
+    <hyperlink ref="F137" r:id="rId132" xr:uid="{F25C4A50-CBE2-4E7A-859B-2FD1E573F254}"/>
+    <hyperlink ref="F138" r:id="rId133" xr:uid="{75FE179B-AF3B-4843-95BD-3EED8C14F364}"/>
+    <hyperlink ref="F139" r:id="rId134" xr:uid="{BE8AAB48-8749-40A3-AC68-AF790396A474}"/>
+    <hyperlink ref="F140" r:id="rId135" xr:uid="{71DD0714-9997-4016-9594-D53081FBA758}"/>
+    <hyperlink ref="F141" r:id="rId136" xr:uid="{7D4236B4-C6D2-4D9E-87D3-21CE2879F2B7}"/>
+    <hyperlink ref="F142" r:id="rId137" xr:uid="{AB78A0F2-0618-4D77-A42C-F41159E73520}"/>
+    <hyperlink ref="F143" r:id="rId138" xr:uid="{951D3B33-2808-4219-B8C0-6A78623E5AA1}"/>
+    <hyperlink ref="F144" r:id="rId139" xr:uid="{A9CE9CF3-160D-4B9F-B8BE-5E531859664C}"/>
+    <hyperlink ref="F145" r:id="rId140" xr:uid="{7A3502EB-AF45-4EE3-88E8-17228934C08E}"/>
+    <hyperlink ref="F146" r:id="rId141" xr:uid="{F89DC979-7339-4628-903D-928FCCCADEE5}"/>
+    <hyperlink ref="F147" r:id="rId142" xr:uid="{D2CACEA3-B167-4FE3-A994-3AD59A20A9A7}"/>
+    <hyperlink ref="F149" r:id="rId143" xr:uid="{22AC07A4-5F12-41FA-8FA8-D4F00424A9EC}"/>
+    <hyperlink ref="F150" r:id="rId144" xr:uid="{357908BA-3A52-4D80-B702-8F516D20FE4D}"/>
+    <hyperlink ref="F151" r:id="rId145" xr:uid="{30560881-6166-4C8F-84C3-DB257B037A99}"/>
+    <hyperlink ref="F152" r:id="rId146" xr:uid="{40EBB7C0-3D94-4005-BF13-1726CA98A382}"/>
+    <hyperlink ref="J146" r:id="rId147" xr:uid="{A0AAB73C-0E04-4F9C-A00E-1ECD18CD39DB}"/>
+    <hyperlink ref="J136" r:id="rId148" xr:uid="{208E28B7-2A86-42C6-8126-3F2AE9DA2E16}"/>
+    <hyperlink ref="J127" r:id="rId149" xr:uid="{3F6E69B2-FCE2-4047-A391-15513C571279}"/>
+    <hyperlink ref="J121" r:id="rId150" xr:uid="{E650C24A-5A75-4844-AD6D-D5FCDBCA2FD3}"/>
+    <hyperlink ref="J120" r:id="rId151" xr:uid="{53678A32-886B-4B53-B546-0001E24DF42B}"/>
+    <hyperlink ref="J109" r:id="rId152" xr:uid="{E1DC4C8B-9DD1-473F-A67A-73E57C61FBD7}"/>
+    <hyperlink ref="J103" r:id="rId153" xr:uid="{C997FC38-26F4-48FB-844F-E3E1FFE2816F}"/>
+    <hyperlink ref="J90" r:id="rId154" xr:uid="{90F477CE-9F50-407B-96D9-A605EBCF5F2A}"/>
+    <hyperlink ref="J82" r:id="rId155" xr:uid="{393AB766-BBE4-4A61-855F-6249FF2F0C00}"/>
+    <hyperlink ref="J80" r:id="rId156" xr:uid="{00370016-38A2-4C03-9FC1-3EDF1695902C}"/>
+    <hyperlink ref="J75" r:id="rId157" xr:uid="{122A37E4-A917-465F-A5E0-908D1D323E26}"/>
+    <hyperlink ref="J70" r:id="rId158" xr:uid="{DB830ECB-F948-4321-B817-3D3B5C974DD3}"/>
+    <hyperlink ref="J60" r:id="rId159" xr:uid="{FCD4D59A-8414-4640-A8A6-26431A8814E3}"/>
+    <hyperlink ref="J57" r:id="rId160" xr:uid="{37BB0F79-60B2-4B00-9FBB-40DF1D28A4ED}"/>
+    <hyperlink ref="J51" r:id="rId161" xr:uid="{0AA0D518-38A6-4E63-A7B1-438D4AB95A1B}"/>
+    <hyperlink ref="J43" r:id="rId162" xr:uid="{8B42E3BE-A086-4470-ABF2-18BD4119F20C}"/>
+    <hyperlink ref="J37" r:id="rId163" xr:uid="{A281819E-447B-44EB-A8E2-1AA4BD68BCB3}"/>
+    <hyperlink ref="J33" r:id="rId164" xr:uid="{F450881D-7ED4-4940-9D56-3587543FEAEE}"/>
+    <hyperlink ref="J32" r:id="rId165" xr:uid="{5E4DF1CD-531A-4950-9A76-3D78246FAB14}"/>
+    <hyperlink ref="J28" r:id="rId166" xr:uid="{A1450CE0-19A3-42D2-AFBD-067A97D78255}"/>
+    <hyperlink ref="J25" r:id="rId167" xr:uid="{3E5231EA-1C06-49C7-AEDC-A7BFA01898F4}"/>
+    <hyperlink ref="J23" r:id="rId168" xr:uid="{766E34A1-3A9B-4ECD-AA67-0D6FAE7081A5}"/>
+    <hyperlink ref="J19" r:id="rId169" xr:uid="{46F03385-8E90-4F39-9030-6E94659E3190}"/>
+    <hyperlink ref="J9" r:id="rId170" xr:uid="{5B5359A7-A23D-48AE-AF45-7AC93A545FD4}"/>
+    <hyperlink ref="J3" r:id="rId171" xr:uid="{8D16C1A8-1D54-4BF6-8C3B-9401171B9C09}"/>
+    <hyperlink ref="F37" r:id="rId172" xr:uid="{5A8751CD-82F0-4AAE-B2E3-E6E30063335F}"/>
+    <hyperlink ref="F38" r:id="rId173" xr:uid="{E7478BB6-64A4-421A-8F94-B9DD4E3DB2C4}"/>
+    <hyperlink ref="F39" r:id="rId174" xr:uid="{51CD7CB0-7E91-47AC-8B01-FCEF92981D1D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
